--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588AEFEF-4218-459B-B109-E65DF9F066B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E95CA7-3404-4C0A-BB17-DB7C7ED36D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="470">
   <si>
     <t>ID</t>
   </si>
@@ -558,9 +558,6 @@
     <t>Plan de trabajo actualizado y compromisos de planificación</t>
   </si>
   <si>
-    <t>Procedimiento de Planificación Lean</t>
-  </si>
-  <si>
     <t>PRO-002</t>
   </si>
   <si>
@@ -576,9 +573,6 @@
     <t>Plan semanal de trabajo y seguimiento de compromisos</t>
   </si>
   <si>
-    <t>Manual Last Planner System</t>
-  </si>
-  <si>
     <t>PRO-003</t>
   </si>
   <si>
@@ -594,9 +588,6 @@
     <t>Restricciones gestionadas y actualizadas</t>
   </si>
   <si>
-    <t>Procedimiento Gestión de Restricciones</t>
-  </si>
-  <si>
     <t>PRO-004</t>
   </si>
   <si>
@@ -612,9 +603,6 @@
     <t>Reportes e indicadores actualizados</t>
   </si>
   <si>
-    <t>Procedimiento de Indicadores LEAN</t>
-  </si>
-  <si>
     <t>PRO-005</t>
   </si>
   <si>
@@ -630,9 +618,6 @@
     <t>Estado actualizado de compromisos y reportes de cumplimiento</t>
   </si>
   <si>
-    <t>Procedimiento Gestión de Actas</t>
-  </si>
-  <si>
     <t>PRO-006</t>
   </si>
   <si>
@@ -648,9 +633,6 @@
     <t>Herramientas actualizadas y soporte funcional</t>
   </si>
   <si>
-    <t>Manual de Herramientas LEAN</t>
-  </si>
-  <si>
     <t>PRO-007</t>
   </si>
   <si>
@@ -666,120 +648,21 @@
     <t>Nuevos desarrollos, automatizaciones y mejoras implementadas</t>
   </si>
   <si>
-    <t>Procedimiento de Desarrollo LEAN</t>
-  </si>
-  <si>
-    <t>Manual de Analytics</t>
-  </si>
-  <si>
-    <t>Manual de Zoho Qntrl</t>
-  </si>
-  <si>
-    <t>Manual de Power BI</t>
-  </si>
-  <si>
-    <t>Procedimiento Last Planner</t>
-  </si>
-  <si>
-    <t>Guía de Preconstrucción</t>
-  </si>
-  <si>
-    <t>Instructivo Centro de Conocimiento LEAN</t>
-  </si>
-  <si>
-    <t>Formato de Actas</t>
-  </si>
-  <si>
-    <t>Formato Pull Planning</t>
-  </si>
-  <si>
-    <t>DOC-001</t>
-  </si>
-  <si>
-    <t>Manual de Usuario</t>
-  </si>
-  <si>
-    <t>SharePoint / Carpeta LEAN</t>
-  </si>
-  <si>
-    <t>1.0</t>
-  </si>
-  <si>
-    <t>DOC-002</t>
-  </si>
-  <si>
-    <t>DOC-003</t>
-  </si>
-  <si>
-    <t>Manual de Zoho Sprints</t>
-  </si>
-  <si>
-    <t>DOC-004</t>
-  </si>
-  <si>
-    <t>Procedimiento de Planificación LEAN</t>
-  </si>
-  <si>
     <t>Procedimiento</t>
   </si>
   <si>
-    <t>DOC-005</t>
-  </si>
-  <si>
-    <t>Procedimiento de Gestión de Restricciones</t>
-  </si>
-  <si>
-    <t>DOC-006</t>
-  </si>
-  <si>
     <t>Instructivo</t>
   </si>
   <si>
-    <t>Repositorio del proyecto</t>
-  </si>
-  <si>
-    <t>DOC-007</t>
-  </si>
-  <si>
-    <t>Manual Dashboard Cumplimiento de Actas</t>
-  </si>
-  <si>
-    <t>Manual Técnico</t>
-  </si>
-  <si>
-    <t>DOC-008</t>
-  </si>
-  <si>
-    <t>Manual Dashboard PPC</t>
-  </si>
-  <si>
-    <t>DOC-009</t>
-  </si>
-  <si>
-    <t>Manual Dashboard PAC</t>
-  </si>
-  <si>
-    <t>DOC-010</t>
-  </si>
-  <si>
-    <t>Formato de Actas de Reunión</t>
-  </si>
-  <si>
     <t>Formato</t>
   </si>
   <si>
-    <t>SharePoint / Formatos</t>
-  </si>
-  <si>
     <t>Coordinar la estrategia del Área LEAN y liderar iniciativas de mejora continua.</t>
   </si>
   <si>
     <t>Área LEAN</t>
   </si>
   <si>
-    <t>Ingeniera LEAN</t>
-  </si>
-  <si>
     <t>Gestionar indicadores, herramientas y procesos Lean.</t>
   </si>
   <si>
@@ -1071,33 +954,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>Camilo</t>
-  </si>
-  <si>
-    <t>https://sprints.zoho.com/workspace/marval2#P163/itemdetails/I102</t>
-  </si>
-  <si>
-    <t>(239) Zoho Sprints - Item Details</t>
-  </si>
-  <si>
-    <t>https://sprints.zoho.com/workspace/marval2#P163/itemdetails/I12/description</t>
-  </si>
-  <si>
-    <t>https://sprints.zoho.com/workspace/marval2#P163/itemdetails/I129</t>
-  </si>
-  <si>
     <t>DEV-003</t>
   </si>
   <si>
     <t>DEV-004</t>
   </si>
   <si>
-    <t>DEV-005</t>
-  </si>
-  <si>
-    <t>DEV-006</t>
-  </si>
-  <si>
     <t>HER-011</t>
   </si>
   <si>
@@ -1264,13 +1126,373 @@
   </si>
   <si>
     <t>MANUAL DE CRITERIOS PARA LA IDENTIFICACIÓN DE RESTRICCIONES EN LPS</t>
+  </si>
+  <si>
+    <t>(URL):https://miro.com/app/dashboard</t>
+  </si>
+  <si>
+    <t>(URL): https://us1.aconex.com/hub/index.html</t>
+  </si>
+  <si>
+    <t>(URL): https://www.youtube.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(URL): </t>
+  </si>
+  <si>
+    <t>(URL): https://produccion.jde.marval.com.co/jde/E1Menu.maf</t>
+  </si>
+  <si>
+    <t>(URL):https://jam.dev/s/c1760f76-7d6f-4108-ba72-628a2ea1b48d</t>
+  </si>
+  <si>
+    <t>(URL): https://crmplus.zoho.com/marval3424/index.do</t>
+  </si>
+  <si>
+    <t>BA-015</t>
+  </si>
+  <si>
+    <t>BA-016</t>
+  </si>
+  <si>
+    <t>BA-023</t>
+  </si>
+  <si>
+    <t>BA-026</t>
+  </si>
+  <si>
+    <t>BA-027</t>
+  </si>
+  <si>
+    <t>BA-028</t>
+  </si>
+  <si>
+    <t>Evaluar el nivel de implementación y madurez de la metodología LEAN en las obras mediante una auditoría estructurada que permita identificar fortalezas, oportunidades de mejora y hacer seguimiento a la evolución de cada proyecto.</t>
+  </si>
+  <si>
+    <t>Integración Sellos de Calidad</t>
+  </si>
+  <si>
+    <t>Módulo que integra la gestión de Sellos de Calidad con el Avance de Grilla, permitiendo validar el cumplimiento de los criterios de calidad durante la ejecución de las actividades. Esta integración mejora la trazabilidad del proceso constructivo, evita reportes de avance sin validación y proporciona información más confiable para el seguimiento de la producción.</t>
+  </si>
+  <si>
+    <t>TICs</t>
+  </si>
+  <si>
+    <t>Módulo desarrollado para optimizar la gestión de restricciones mediante la automatización de reglas de negocio y la parametrización de actividades. Incorpora funcionalidades para la creación, administración, liberación y eliminación de restricciones, así como la edición controlada de fechas de inicio de fabricación y legalización, actualización de acuerdos de servicio, modificación de subtipos y atributos de las actividades, garantizando una programación más flexible, trazable y alineada con el proceso constructivo.</t>
+  </si>
+  <si>
+    <t>Automatización de Restricciones</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b6</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b7</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b8</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b9</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b10</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b11</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b12</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b13</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b14</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b15</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b16</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b17</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b18</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b19</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b20</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b21</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b22</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b23</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b24</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b25</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b26</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b27</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b28</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b29</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b30</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b31</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b32</t>
+  </si>
+  <si>
+    <t>Duplicidad de avances dos clicks en guardar todo en reportar avance</t>
+  </si>
+  <si>
+    <t>Por agregar</t>
+  </si>
+  <si>
+    <t>Agregar CNC en reporte preliminar</t>
+  </si>
+  <si>
+    <t>Cuando se incumple una restricción, observacion y no cumplimiento debe serobligatorio</t>
+  </si>
+  <si>
+    <t>Last Planner</t>
+  </si>
+  <si>
+    <t>Crear historia</t>
+  </si>
+  <si>
+    <t>CNC cuando se hace reducción</t>
+  </si>
+  <si>
+    <t>Avances</t>
+  </si>
+  <si>
+    <t>Implentar</t>
+  </si>
+  <si>
+    <t>Se desconecta las unidades con las tareas, activar la bandera por proyectos para hacerlo nacional (SE DEBE VALDIAR SI TIENE UNIDADES PERDIDAS, LEAN DEBE DEFINIR CUALES SON)</t>
+  </si>
+  <si>
+    <t>BA-030</t>
+  </si>
+  <si>
+    <t>BA-031</t>
+  </si>
+  <si>
+    <t>BA-032</t>
+  </si>
+  <si>
+    <t>BA-033</t>
+  </si>
+  <si>
+    <t>BA-034</t>
+  </si>
+  <si>
+    <t>Daniela</t>
+  </si>
+  <si>
+    <t>Avance fuera de reunión Last Planner (Número de caso 85972)</t>
+  </si>
+  <si>
+    <t>Caso (#85972) - AVANCE FUERA DE REUNION LAST PLANNER - GLPI</t>
+  </si>
+  <si>
+    <t>Avance por fuera de reunión Last Palnner (Número de caso 85977)</t>
+  </si>
+  <si>
+    <t>Caso (#85977) - AVANCE FUERA DE REUNION LAST PLANNER - GLPI</t>
+  </si>
+  <si>
+    <t>No carga información tablero de rendimientos proyecto Provenza Regency (Número de caso 93460)</t>
+  </si>
+  <si>
+    <t>Caso (#93460) - No carga información tablero de rendimientos proyecto Provenza Regency - GLPI</t>
+  </si>
+  <si>
+    <t>Incidencia en el momento de reportar avances (Número de caso 93306)</t>
+  </si>
+  <si>
+    <t>Caso (#93306) - Incidencia en el momento de reportar avances - GLPI</t>
+  </si>
+  <si>
+    <t>Integración para el funcionamiento de grilla para torres altas que se entreguen una sola torre en estapas diferentes (Número de caso 68339)</t>
+  </si>
+  <si>
+    <t>Caso (#68339) - Integración para el funcionamiento de grilla para torres altas que se entreguen unas sola torrre en etapas diferentes - GLPI</t>
+  </si>
+  <si>
+    <t>Acta semanal Country Park (Número de caso 93394)</t>
+  </si>
+  <si>
+    <t>Caso (#93394) - ACTA SEMANAL COUNTRY PARK - GLPI</t>
+  </si>
+  <si>
+    <t>BA-035</t>
+  </si>
+  <si>
+    <t>BA-036</t>
+  </si>
+  <si>
+    <t>BA-037</t>
+  </si>
+  <si>
+    <t>BA-038</t>
+  </si>
+  <si>
+    <t>BA-039</t>
+  </si>
+  <si>
+    <t>BA-040</t>
+  </si>
+  <si>
+    <t>Paola-Daniela</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b33</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b34</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b35</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b36</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b37</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b38</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b39</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b40</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b41</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b42</t>
+  </si>
+  <si>
+    <t>https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b43</t>
+  </si>
+  <si>
+    <t>Herramienta utilizada para la planificación, programación y seguimiento de cronogramas de proyectos, permitiendo analizar rutas críticas, duraciones y secuencia de actividades en apoyo a la gestión de obra.</t>
+  </si>
+  <si>
+    <t>Plataforma colaborativa empleada para la construcción de diagramas, mapas de procesos, sesiones de ideación, talleres LEAN y documentación visual de iniciativas de mejora continua.</t>
+  </si>
+  <si>
+    <t>Plataforma utilizada para registrar, gestionar y dar seguimiento a los requerimientos, incidencias y solicitudes de desarrollo del Área LEAN, facilitando la trazabilidad de las iniciativas.</t>
+  </si>
+  <si>
+    <t>Plataforma de gestión documental utilizada para administrar, consultar y controlar la información técnica de los proyectos, garantizando la trazabilidad de documentos, planos y comunicaciones.</t>
+  </si>
+  <si>
+    <t>Repositorio de apoyo para la consulta de capacitaciones, tutoriales y material audiovisual relacionado con metodologías LEAN, herramientas tecnológicas y procesos internos.</t>
+  </si>
+  <si>
+    <t>Sistema ERP corporativo utilizado para consultar información administrativa y operativa relacionada con proyectos, contratos, presupuestos y demás procesos empresariales que apoyan la gestión del Área LEAN.</t>
+  </si>
+  <si>
+    <t>Herramienta que permite establecer una conexión segura a la red corporativa para acceder de forma remota a aplicaciones, servidores y recursos internos utilizados por el Área LEAN.</t>
+  </si>
+  <si>
+    <t>Extensión de captura de pantalla y grabación de video utilizada para documentar incidencias y registrar evidencias funcionales de Analytics, apoyando el proceso de reporte y seguimiento de desarrollos.</t>
+  </si>
+  <si>
+    <t>Planificación</t>
+  </si>
+  <si>
+    <t>Colaboración</t>
+  </si>
+  <si>
+    <t>Gestion de Requerimientos</t>
+  </si>
+  <si>
+    <t>Gestión Documental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitación </t>
+  </si>
+  <si>
+    <t>ERP</t>
+  </si>
+  <si>
+    <t>Captura de Evidencia</t>
+  </si>
+  <si>
+    <t>Accceso Remoto</t>
+  </si>
+  <si>
+    <t>Permalink acuerdos de servicio subidos 2025</t>
+  </si>
+  <si>
+    <t>https://analytics.zoho.com/open-view/1954380000086356866/fd969ba42dcccf08d3ddc846df8aacb76bbb39393f3fdb983c18b28d21853599</t>
+  </si>
+  <si>
+    <t>IND-007</t>
+  </si>
+  <si>
+    <t>Analytics Zoho</t>
+  </si>
+  <si>
+    <t>Dashboard que consolida y visualiza indicadores de desempeño de los proyectos, permitiendo realizar seguimiento al cumplimiento de metas, analizar tendencias y apoyar la toma de decisiones del Área LEAN.</t>
+  </si>
+  <si>
+    <t>Indicador que permite consultar y verificar los acuerdos de servicio cargados en la plataforma mediante enlaces permanentes (permalinks), facilitando el acceso, control y seguimiento de la información por parte del Área LEAN.</t>
+  </si>
+  <si>
+    <t>IND-008</t>
+  </si>
+  <si>
+    <t>Permalink contratos teoricos vs contratos reales</t>
+  </si>
+  <si>
+    <t>Reporte que permite comparar los contratos teóricos definidos en la programación con los contratos reales registrados en el proyecto, facilitando la identificación de diferencias, el seguimiento de la contratación y la validación de la información utilizada por el Área LEAN.</t>
+  </si>
+  <si>
+    <t>https://analytics.zoho.com/open-view/1954380000102979448/88cda4660a1127929863753bced064f2</t>
+  </si>
+  <si>
+    <t>Ingeniero LEAN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1283,6 +1505,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
@@ -1299,12 +1522,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1370,9 +1587,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1384,9 +1601,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1397,22 +1611,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1439,13 +1659,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1487,13 +1707,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2166,12 +2386,18 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>345</v>
+        <v>299</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>443</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2179,20 +2405,26 @@
       <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>341</v>
+        <v>295</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>346</v>
+        <v>300</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>444</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2200,20 +2432,26 @@
       <c r="F13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="G13" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>342</v>
+        <v>296</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>347</v>
+        <v>301</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>445</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2221,20 +2459,26 @@
       <c r="F14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G14" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>343</v>
+        <v>297</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>348</v>
+        <v>302</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2242,20 +2486,26 @@
       <c r="F15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="3" t="s">
+      <c r="G15" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>349</v>
+        <v>303</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>447</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2263,20 +2513,26 @@
       <c r="F16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="G16" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>350</v>
+        <v>304</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>448</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2284,20 +2540,26 @@
       <c r="F17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="G17" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>352</v>
+        <v>306</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>353</v>
+        <v>307</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2305,20 +2567,26 @@
       <c r="F18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H18" s="3" t="s">
+      <c r="G18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>354</v>
+        <v>308</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>449</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2326,29 +2594,29 @@
       <c r="F19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" s="3" t="s">
+      <c r="G19" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>35</v>
       </c>
       <c r="I19" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="25" customWidth="1"/>
+    <col min="1" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2362,206 +2630,131 @@
         <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>306</v>
+        <v>130</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>329</v>
+        <v>33</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>331</v>
+        <v>125</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>115</v>
+      <c r="B3" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>329</v>
+        <v>363</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>330</v>
+        <v>292</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="G4" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
+        <v>293</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>368</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" t="s">
-        <v>329</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="G5" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" t="s">
-        <v>329</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>372</v>
-      </c>
-      <c r="D9" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>125</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" location="P163/itemdetails/I102" xr:uid="{4F14EE80-AC72-4FD9-AD96-DF8C921FE23E}"/>
-  </hyperlinks>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124371BC-E72D-4ACB-81AC-BC0F07668931}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -2597,383 +2790,903 @@
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>325</v>
+        <v>286</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>310</v>
+        <v>271</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>314</v>
+        <v>275</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>316</v>
+        <v>277</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>319</v>
+        <v>276</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>322</v>
+        <v>283</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>307</v>
+        <v>268</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G26" t="s">
+        <v>289</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G27" t="s">
+        <v>289</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G28" t="s">
+        <v>289</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="I30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B31" t="s">
+        <v>398</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B32" t="s">
+        <v>398</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G32" t="s">
+        <v>289</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="I32" t="s">
+        <v>401</v>
+      </c>
+      <c r="J32" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B33" t="s">
+        <v>398</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G33" t="s">
+        <v>289</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="I33" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B34" t="s">
+        <v>405</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G35" t="s">
+        <v>289</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="I35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B36" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G36" t="s">
+        <v>289</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="I36" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B37" t="s">
+        <v>418</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G37" t="s">
+        <v>289</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="I37" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B38" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G38" t="s">
+        <v>289</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="I38" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B39" t="s">
+        <v>422</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G39" t="s">
+        <v>289</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="I39" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B40" t="s">
+        <v>424</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G40" t="s">
+        <v>289</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="I40" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{CBBFCFAD-F2B4-49E6-AFA2-A2E8E2BEFE02}"/>
+    <hyperlink ref="H3:H29" r:id="rId2" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{B39A16E9-AB55-4A33-AF19-64F1A9B41477}"/>
+    <hyperlink ref="H30:H40" r:id="rId3" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{AC1F786A-C574-4F44-A7A1-294557B49834}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="25" customWidth="1"/>
@@ -3076,6 +3789,9 @@
       <c r="F4" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="G4" t="s">
+        <v>154</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>146</v>
       </c>
@@ -3111,7 +3827,7 @@
         <v>151</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>377</v>
+        <v>331</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
@@ -3132,16 +3848,19 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>376</v>
+        <v>330</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>463</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
@@ -3152,11 +3871,61 @@
         <v>154</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>378</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{3DE1C176-35E1-43D9-ACB2-74C19F9566B0}"/>
+    <hyperlink ref="G9" r:id="rId2" xr:uid="{855EDAB8-B1EA-4B35-ABA0-9BBA4A35E2E4}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3211,163 +3980,166 @@
       <c r="F2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>166</v>
+      <c r="G3" s="17" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>184</v>
+        <v>179</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G8" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G3" r:id="rId1" xr:uid="{E450CA4A-B2D1-4690-B3E1-010CCC902B44}"/>
+    <hyperlink ref="G6" r:id="rId2" xr:uid="{95B4B31C-CB0B-4481-8BDB-D15000630CDB}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{1304D265-C734-41FD-B0DC-79EE4DF3EB3C}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{7859DA98-00F2-428D-8A15-DBB023397F25}"/>
+    <hyperlink ref="G7" r:id="rId5" xr:uid="{0F00771F-5197-40C4-8FA1-598441B6B712}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3390,444 +4162,188 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G2" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>206</v>
+      <c r="E2" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>191</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G3" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>314</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="G3" s="5">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>190</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G4" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="E4" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="G4" s="5">
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>212</v>
+        <v>338</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>213</v>
+        <v>337</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>214</v>
+        <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G5" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L5" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>345</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G6" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="E6" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" t="s">
+        <v>342</v>
+      </c>
+      <c r="G6" s="5">
+        <v>44697</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>346</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G7" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="E7" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="F7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G7" s="5">
+        <v>44697</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>221</v>
+        <v>347</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>349</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>219</v>
+      <c r="E8" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G8" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G9" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G10" s="6">
-        <v>46216</v>
-      </c>
-      <c r="L10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G11" s="6">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="G13" s="6">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="G14" s="6">
+        <v>348</v>
+      </c>
+      <c r="G8" s="5">
         <v>45757</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>386</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>387</v>
-      </c>
-      <c r="F16" t="s">
-        <v>388</v>
-      </c>
-      <c r="G16" s="6">
-        <v>44697</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>389</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>390</v>
-      </c>
-      <c r="F17" t="s">
-        <v>388</v>
-      </c>
-      <c r="G17" s="6">
-        <v>44697</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>395</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="G18" s="6">
-        <v>45757</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E19" s="14"/>
-    </row>
-    <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-    </row>
-    <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="15"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="13"/>
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E12" r:id="rId1" xr:uid="{CD1E00D1-0B72-42F3-80DA-BD697F689749}"/>
-    <hyperlink ref="E15" r:id="rId2" xr:uid="{BE2AE314-3341-4469-ADFD-A92FCDCAD2AD}"/>
-    <hyperlink ref="B18" r:id="rId3" display="https://us1.aconex.com/rsrc/20260702.0843/es_ES_DOC/document/view/index.html?ControlledDocument_ID=1353331688403523199&amp;ControlledDocument_projectID=1207968420&amp;VIEW_CD_RETURN_URL=%2FSearchControlledDoc%3FSESSION_SAVE_DOCUMENTNO%3D%26SESSION_SAVE_TITLE%3D%2B%26SESSION_SAVE_REVISION%3D%2B%26SESSION_SAVE_STATUS%3D0%26SESSION_SAVE_TYPE%3D0%26SESSION_SAVE_DISCIPLINE%3Dnull%26SESSION_CREATION_DATE%3Dnull%26SESSION_REVISION_DATE%3Dnull%26SESSION_SAVE_REVIEW_DATE%3Dnull%26SESSION_SAVE_REVIEWED_DATE%3Dnull%26SESSION_SAVE_AUTHOR%3Dnull%26SESSION_SAVE_FILETYPE%3Dnull%26SESSION_REFERENCE%3Dnull%26SESSION_SAVE_FOLDER_PATH%3D%26SESSION_SAVE_ALL_REVS%3Dnull%26SESSION_SAVE_SORT_DIR%3DASC%26SESSION_SAVE_SORT_FIELD%3Ddocno%26SESSION_SHARED_TO%3D-1%26SESSION_LINKED_TO_PUBLIC%3D0" xr:uid="{B33F7C5F-686F-4168-AEFA-38B03829F34C}"/>
-    <hyperlink ref="E18" r:id="rId4" display="https://us1.aconex.com/ViewDoc?trackingid=1353331688098790961&amp;projectid=1207968420&amp;cversion=1&amp;tab=0" xr:uid="{3A60C185-9CFD-414E-8CB5-584B4E40E318}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{CD1E00D1-0B72-42F3-80DA-BD697F689749}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{BE2AE314-3341-4469-ADFD-A92FCDCAD2AD}"/>
+    <hyperlink ref="B8" r:id="rId3" display="https://us1.aconex.com/rsrc/20260702.0843/es_ES_DOC/document/view/index.html?ControlledDocument_ID=1353331688403523199&amp;ControlledDocument_projectID=1207968420&amp;VIEW_CD_RETURN_URL=%2FSearchControlledDoc%3FSESSION_SAVE_DOCUMENTNO%3D%26SESSION_SAVE_TITLE%3D%2B%26SESSION_SAVE_REVISION%3D%2B%26SESSION_SAVE_STATUS%3D0%26SESSION_SAVE_TYPE%3D0%26SESSION_SAVE_DISCIPLINE%3Dnull%26SESSION_CREATION_DATE%3Dnull%26SESSION_REVISION_DATE%3Dnull%26SESSION_SAVE_REVIEW_DATE%3Dnull%26SESSION_SAVE_REVIEWED_DATE%3Dnull%26SESSION_SAVE_AUTHOR%3Dnull%26SESSION_SAVE_FILETYPE%3Dnull%26SESSION_REFERENCE%3Dnull%26SESSION_SAVE_FOLDER_PATH%3D%26SESSION_SAVE_ALL_REVS%3Dnull%26SESSION_SAVE_SORT_DIR%3DASC%26SESSION_SAVE_SORT_FIELD%3Ddocno%26SESSION_SHARED_TO%3D-1%26SESSION_LINKED_TO_PUBLIC%3D0" xr:uid="{B33F7C5F-686F-4168-AEFA-38B03829F34C}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{3A60C185-9CFD-414E-8CB5-584B4E40E318}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{F6E3CF0D-17C9-4F23-A241-03FF5ABD0FEF}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -3851,7 +4367,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -3865,358 +4381,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>239</v>
+        <v>193</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>240</v>
+        <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>233</v>
+        <v>469</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>242</v>
+        <v>195</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>246</v>
+        <v>210</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>244</v>
+        <v>205</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>247</v>
+        <v>210</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>233</v>
+        <v>469</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="7"/>
+        <v>195</v>
+      </c>
+      <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>232</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>251</v>
+        <v>210</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>253</v>
+        <v>210</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>365</v>
+        <v>319</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>366</v>
+        <v>210</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>271</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>275</v>
+      <c r="A19" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>276</v>
+        <v>231</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>268</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E95CA7-3404-4C0A-BB17-DB7C7ED36D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315ED28-9EF0-46AB-BD00-5120F724EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Roadmap" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="470">
   <si>
     <t>ID</t>
   </si>
@@ -1589,7 +1590,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1627,9 +1628,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2754,21 +2752,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124371BC-E72D-4ACB-81AC-BC0F07668931}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2779,25 +2776,22 @@
         <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>238</v>
       </c>
@@ -2807,20 +2801,20 @@
       <c r="C2" s="2" t="s">
         <v>239</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G2" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>241</v>
       </c>
@@ -2830,20 +2824,20 @@
       <c r="C3" s="2" t="s">
         <v>242</v>
       </c>
+      <c r="D3" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E3" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G3" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>243</v>
       </c>
@@ -2853,20 +2847,20 @@
       <c r="C4" s="2" t="s">
         <v>244</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G4" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>245</v>
       </c>
@@ -2876,20 +2870,20 @@
       <c r="C5" s="2" t="s">
         <v>246</v>
       </c>
+      <c r="D5" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G5" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>247</v>
       </c>
@@ -2899,20 +2893,20 @@
       <c r="C6" s="2" t="s">
         <v>248</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G6" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>249</v>
       </c>
@@ -2922,20 +2916,20 @@
       <c r="C7" s="2" t="s">
         <v>250</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G7" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>251</v>
       </c>
@@ -2945,20 +2939,20 @@
       <c r="C8" s="2" t="s">
         <v>252</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G8" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -2968,20 +2962,20 @@
       <c r="C9" s="2" t="s">
         <v>254</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>255</v>
       </c>
@@ -2991,20 +2985,20 @@
       <c r="C10" s="2" t="s">
         <v>256</v>
       </c>
+      <c r="D10" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E10" s="2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G10" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>257</v>
       </c>
@@ -3014,20 +3008,20 @@
       <c r="C11" s="2" t="s">
         <v>258</v>
       </c>
+      <c r="D11" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G11" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>259</v>
       </c>
@@ -3037,20 +3031,20 @@
       <c r="C12" s="2" t="s">
         <v>260</v>
       </c>
+      <c r="D12" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E12" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G12" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>261</v>
       </c>
@@ -3060,20 +3054,20 @@
       <c r="C13" s="2" t="s">
         <v>262</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G13" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>263</v>
       </c>
@@ -3083,20 +3077,20 @@
       <c r="C14" s="2" t="s">
         <v>264</v>
       </c>
+      <c r="D14" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G14" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>265</v>
       </c>
@@ -3106,20 +3100,20 @@
       <c r="C15" s="2" t="s">
         <v>266</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G15" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>357</v>
       </c>
@@ -3129,20 +3123,20 @@
       <c r="C16" s="2" t="s">
         <v>271</v>
       </c>
+      <c r="D16" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E16" s="2" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G16" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>358</v>
       </c>
@@ -3152,20 +3146,20 @@
       <c r="C17" s="2" t="s">
         <v>273</v>
       </c>
+      <c r="D17" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E17" s="2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G17" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>270</v>
       </c>
@@ -3175,20 +3169,20 @@
       <c r="C18" s="2" t="s">
         <v>275</v>
       </c>
+      <c r="D18" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>240</v>
+        <v>287</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G18" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>272</v>
       </c>
@@ -3198,20 +3192,20 @@
       <c r="C19" s="2" t="s">
         <v>277</v>
       </c>
+      <c r="D19" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="E19" s="2" t="s">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G19" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>274</v>
       </c>
@@ -3221,17 +3215,17 @@
       <c r="C20" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>276</v>
       </c>
@@ -3241,17 +3235,17 @@
       <c r="C21" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>278</v>
       </c>
@@ -3261,17 +3255,17 @@
       <c r="C22" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>280</v>
       </c>
@@ -3281,17 +3275,17 @@
       <c r="C23" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>359</v>
       </c>
@@ -3301,20 +3295,20 @@
       <c r="C24" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>282</v>
       </c>
@@ -3324,20 +3318,20 @@
       <c r="C25" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="H25" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>284</v>
       </c>
@@ -3347,20 +3341,20 @@
       <c r="C26" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="D26" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G26" t="s">
+      <c r="F26" t="s">
         <v>289</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="I26" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>360</v>
       </c>
@@ -3370,20 +3364,20 @@
       <c r="C27" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="D27" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G27" t="s">
+      <c r="F27" t="s">
         <v>289</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>361</v>
       </c>
@@ -3393,60 +3387,60 @@
       <c r="C28" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="D28" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G28" t="s">
+      <c r="F28" t="s">
         <v>289</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="G28" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="I28" s="8" t="s">
+      <c r="H28" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>362</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="D29" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="H29" s="8" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>407</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="D30" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="G30" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="I30" t="s">
+      <c r="H30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>408</v>
       </c>
@@ -3456,17 +3450,17 @@
       <c r="C31" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="D31" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>409</v>
       </c>
@@ -3476,23 +3470,23 @@
       <c r="C32" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="D32" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G32" t="s">
+      <c r="F32" t="s">
         <v>289</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="G32" s="6" t="s">
         <v>434</v>
       </c>
+      <c r="H32" t="s">
+        <v>401</v>
+      </c>
       <c r="I32" t="s">
-        <v>401</v>
-      </c>
-      <c r="J32" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>410</v>
       </c>
@@ -3502,20 +3496,20 @@
       <c r="C33" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="D33" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G33" t="s">
+      <c r="F33" t="s">
         <v>289</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="I33" t="s">
+      <c r="H33" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>411</v>
       </c>
@@ -3525,17 +3519,17 @@
       <c r="C34" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="D34" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>425</v>
       </c>
@@ -3545,20 +3539,20 @@
       <c r="C35" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="D35" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G35" t="s">
+      <c r="F35" t="s">
         <v>289</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="I35" t="s">
+      <c r="H35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>426</v>
       </c>
@@ -3568,20 +3562,20 @@
       <c r="C36" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="D36" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G36" t="s">
+      <c r="F36" t="s">
         <v>289</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="I36" t="s">
+      <c r="H36" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>427</v>
       </c>
@@ -3591,20 +3585,20 @@
       <c r="C37" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="D37" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G37" t="s">
+      <c r="F37" t="s">
         <v>289</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="I37" t="s">
+      <c r="H37" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>428</v>
       </c>
@@ -3614,20 +3608,20 @@
       <c r="C38" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G38" t="s">
+      <c r="F38" t="s">
         <v>289</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="G38" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="I38" t="s">
+      <c r="H38" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>429</v>
       </c>
@@ -3637,20 +3631,20 @@
       <c r="C39" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E39" s="8" t="s">
+      <c r="D39" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G39" t="s">
+      <c r="F39" t="s">
         <v>289</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="G39" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="I39" t="s">
+      <c r="H39" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>430</v>
       </c>
@@ -3660,25 +3654,25 @@
       <c r="C40" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="D40" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G40" t="s">
+      <c r="F40" t="s">
         <v>289</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="G40" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="I40" t="s">
+      <c r="H40" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{CBBFCFAD-F2B4-49E6-AFA2-A2E8E2BEFE02}"/>
-    <hyperlink ref="H3:H29" r:id="rId2" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{B39A16E9-AB55-4A33-AF19-64F1A9B41477}"/>
-    <hyperlink ref="H30:H40" r:id="rId3" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{AC1F786A-C574-4F44-A7A1-294557B49834}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{CBBFCFAD-F2B4-49E6-AFA2-A2E8E2BEFE02}"/>
+    <hyperlink ref="G3:G29" r:id="rId2" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{B39A16E9-AB55-4A33-AF19-64F1A9B41477}"/>
+    <hyperlink ref="G30:G40" r:id="rId3" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{AC1F786A-C574-4F44-A7A1-294557B49834}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3980,7 +3974,7 @@
       <c r="F2" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -4001,7 +3995,7 @@
       <c r="F3" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4024,7 +4018,7 @@
       <c r="F4" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>344</v>
       </c>
     </row>
@@ -4047,7 +4041,7 @@
       <c r="F5" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4070,7 +4064,7 @@
       <c r="F6" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4093,7 +4087,7 @@
       <c r="F7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="16" t="s">
         <v>317</v>
       </c>
     </row>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D315ED28-9EF0-46AB-BD00-5120F724EB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4551322A-836E-43F8-A4B3-081D8144DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -1414,9 +1414,6 @@
     <t>Plataforma colaborativa empleada para la construcción de diagramas, mapas de procesos, sesiones de ideación, talleres LEAN y documentación visual de iniciativas de mejora continua.</t>
   </si>
   <si>
-    <t>Plataforma utilizada para registrar, gestionar y dar seguimiento a los requerimientos, incidencias y solicitudes de desarrollo del Área LEAN, facilitando la trazabilidad de las iniciativas.</t>
-  </si>
-  <si>
     <t>Plataforma de gestión documental utilizada para administrar, consultar y controlar la información técnica de los proyectos, garantizando la trazabilidad de documentos, planos y comunicaciones.</t>
   </si>
   <si>
@@ -1487,6 +1484,9 @@
   </si>
   <si>
     <t>Ingeniero LEAN</t>
+  </si>
+  <si>
+    <t>Zoho CRM es una plataforma que permite visualizar el estado actual del cliente en el proceso de la vivienda, proporcionando información clave para orientar el alistamiento oportuno de las viviendas.</t>
   </si>
 </sst>
 </file>
@@ -2392,7 +2392,7 @@
         <v>299</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>443</v>
@@ -2419,7 +2419,7 @@
         <v>300</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>444</v>
@@ -2446,10 +2446,10 @@
         <v>301</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2473,10 +2473,10 @@
         <v>302</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2500,10 +2500,10 @@
         <v>303</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2527,10 +2527,10 @@
         <v>304</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2554,10 +2554,10 @@
         <v>307</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2581,10 +2581,10 @@
         <v>308</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -3853,7 +3853,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -3870,16 +3870,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -3888,21 +3888,21 @@
         <v>291</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -3911,7 +3911,7 @@
         <v>291</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -4398,7 +4398,7 @@
         <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>202</v>
@@ -4456,7 +4456,7 @@
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>199</v>
@@ -4534,7 +4534,7 @@
         <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>216</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4551322A-836E-43F8-A4B3-081D8144DB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94FC8E4-F69D-43E1-B5A7-EA405E16BEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1450,9 +1450,6 @@
     <t>Captura de Evidencia</t>
   </si>
   <si>
-    <t>Accceso Remoto</t>
-  </si>
-  <si>
     <t>Permalink acuerdos de servicio subidos 2025</t>
   </si>
   <si>
@@ -1487,6 +1484,9 @@
   </si>
   <si>
     <t>Zoho CRM es una plataforma que permite visualizar el estado actual del cliente en el proceso de la vivienda, proporcionando información clave para orientar el alistamiento oportuno de las viviendas.</t>
+  </si>
+  <si>
+    <t>Acceso Remoto</t>
   </si>
 </sst>
 </file>
@@ -2449,7 +2449,7 @@
         <v>452</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2581,7 +2581,7 @@
         <v>308</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>448</v>
@@ -3853,7 +3853,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -3870,16 +3870,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>461</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -3888,21 +3888,21 @@
         <v>291</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -3911,7 +3911,7 @@
         <v>291</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -4398,7 +4398,7 @@
         <v>201</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>202</v>
@@ -4456,7 +4456,7 @@
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>199</v>
@@ -4534,7 +4534,7 @@
         <v>215</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>216</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94FC8E4-F69D-43E1-B5A7-EA405E16BEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A5DD35-BA16-427F-9D50-5809E8403F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,9 +208,6 @@
     <t>Sotec</t>
   </si>
   <si>
-    <t>Plataforma utilizada para la consulta y gestión de información técnica y operativa de los proyectos.</t>
-  </si>
-  <si>
     <t>Acceso según permisos corporativos.</t>
   </si>
   <si>
@@ -1487,6 +1484,9 @@
   </si>
   <si>
     <t>Acceso Remoto</t>
+  </si>
+  <si>
+    <t>Herramienta de apoyo que permite reportar fallas, registrar solicitudes y proponer mejoras relacionadas con las herramientas y plataformas utilizadas en la compañía.</t>
   </si>
 </sst>
 </file>
@@ -2114,7 +2114,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>35</v>
@@ -2143,7 +2143,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>35</v>
@@ -2152,7 +2152,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>469</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2172,27 +2172,27 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2201,27 +2201,27 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2230,27 +2230,27 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -2259,27 +2259,27 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2288,27 +2288,27 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -2317,27 +2317,27 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2346,27 +2346,27 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2375,27 +2375,27 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2404,7 +2404,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -2413,16 +2413,16 @@
     </row>
     <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2431,7 +2431,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>35</v>
@@ -2440,16 +2440,16 @@
     </row>
     <row r="14" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2458,7 +2458,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>35</v>
@@ -2467,16 +2467,16 @@
     </row>
     <row r="15" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2485,7 +2485,7 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>35</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="16" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2512,7 +2512,7 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>35</v>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="17" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2539,7 +2539,7 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>35</v>
@@ -2548,16 +2548,16 @@
     </row>
     <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2566,7 +2566,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>35</v>
@@ -2575,16 +2575,16 @@
     </row>
     <row r="19" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2593,7 +2593,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>35</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2642,106 +2642,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>326</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>327</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>365</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>366</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2793,760 +2793,760 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>266</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>432</v>
-      </c>
       <c r="H30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B31" t="s">
+        <v>397</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B32" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F32" t="s">
+        <v>288</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="H32" t="s">
         <v>400</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="F32" t="s">
-        <v>289</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>401</v>
-      </c>
-      <c r="I32" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B33" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="F33" t="s">
+        <v>288</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="H33" t="s">
         <v>403</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="F33" t="s">
-        <v>289</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>435</v>
-      </c>
-      <c r="H33" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B34" t="s">
+        <v>404</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B35" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H35" t="s">
         <v>42</v>
@@ -3554,22 +3554,22 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B36" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H36" t="s">
         <v>42</v>
@@ -3577,22 +3577,22 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B37" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H37" t="s">
         <v>42</v>
@@ -3600,22 +3600,22 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H38" t="s">
         <v>42</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H39" t="s">
         <v>42</v>
@@ -3646,22 +3646,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B40" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H40" t="s">
         <v>42</v>
@@ -3714,204 +3714,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="G2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -3957,158 +3957,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G3" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="G4" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="G5" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G6" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="G7" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4158,45 +4158,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>316</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4227,33 +4227,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4262,10 +4262,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="F6" t="s">
         <v>341</v>
-      </c>
-      <c r="F6" t="s">
-        <v>342</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4285,10 +4285,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4308,10 +4308,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4361,7 +4361,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4375,358 +4375,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>203</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>214</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>320</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>218</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>220</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>322</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>324</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>232</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>237</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -4782,60 +4782,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A5DD35-BA16-427F-9D50-5809E8403F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD6803C-58EC-4B6D-9E2C-DAD1C20E4545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -208,9 +208,6 @@
     <t>Sotec</t>
   </si>
   <si>
-    <t>Acceso según permisos corporativos.</t>
-  </si>
-  <si>
     <t>HER-004</t>
   </si>
   <si>
@@ -1487,6 +1484,9 @@
   </si>
   <si>
     <t>Herramienta de apoyo que permite reportar fallas, registrar solicitudes y proponer mejoras relacionadas con las herramientas y plataformas utilizadas en la compañía.</t>
+  </si>
+  <si>
+    <t>Las solicitudes deben registrarse con una descripción clara, evidencias (si aplica) y el impacto generado para facilitar su análisis y atención.</t>
   </si>
 </sst>
 </file>
@@ -2114,7 +2114,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>35</v>
@@ -2143,7 +2143,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>35</v>
@@ -2163,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2172,27 +2172,27 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>469</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2201,27 +2201,27 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2230,27 +2230,27 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -2259,27 +2259,27 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2288,27 +2288,27 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -2317,27 +2317,27 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2346,27 +2346,27 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2375,27 +2375,27 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2404,7 +2404,7 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -2413,16 +2413,16 @@
     </row>
     <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2431,7 +2431,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>35</v>
@@ -2440,16 +2440,16 @@
     </row>
     <row r="14" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2458,7 +2458,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>35</v>
@@ -2467,16 +2467,16 @@
     </row>
     <row r="15" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2485,7 +2485,7 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>35</v>
@@ -2494,16 +2494,16 @@
     </row>
     <row r="16" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2512,7 +2512,7 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>35</v>
@@ -2521,16 +2521,16 @@
     </row>
     <row r="17" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2539,7 +2539,7 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>35</v>
@@ -2548,16 +2548,16 @@
     </row>
     <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2566,7 +2566,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>35</v>
@@ -2575,16 +2575,16 @@
     </row>
     <row r="19" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2593,7 +2593,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>35</v>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2642,106 +2642,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>364</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>365</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -2770,10 +2770,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2793,760 +2793,760 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B28" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>431</v>
-      </c>
       <c r="H30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B31" t="s">
+        <v>396</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B32" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F32" t="s">
+        <v>287</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="H32" t="s">
         <v>399</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F32" t="s">
-        <v>288</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>400</v>
-      </c>
-      <c r="I32" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B33" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F33" t="s">
+        <v>287</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="H33" t="s">
         <v>402</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="F33" t="s">
-        <v>288</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="H33" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B34" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H35" t="s">
         <v>42</v>
@@ -3554,22 +3554,22 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B36" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H36" t="s">
         <v>42</v>
@@ -3577,22 +3577,22 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B37" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F37" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H37" t="s">
         <v>42</v>
@@ -3600,22 +3600,22 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B38" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F38" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H38" t="s">
         <v>42</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F39" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H39" t="s">
         <v>42</v>
@@ -3646,22 +3646,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B40" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H40" t="s">
         <v>42</v>
@@ -3714,204 +3714,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="G2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -3957,158 +3957,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="G3" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G4" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="G5" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="G6" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="G7" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4158,45 +4158,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>315</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4227,33 +4227,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4262,10 +4262,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="F6" t="s">
         <v>340</v>
-      </c>
-      <c r="F6" t="s">
-        <v>341</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4273,10 +4273,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4285,10 +4285,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4296,10 +4296,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4308,10 +4308,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4361,7 +4361,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4375,358 +4375,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>211</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>213</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>319</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>219</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>221</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>223</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>321</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>236</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4782,60 +4782,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD6803C-58EC-4B6D-9E2C-DAD1C20E4545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9110CCE-2EA8-4B5D-B709-08B9037250AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="469">
   <si>
     <t>ID</t>
   </si>
@@ -184,9 +184,6 @@
     <t>Activo</t>
   </si>
   <si>
-    <t>(Ruta al manual)</t>
-  </si>
-  <si>
     <t>Uso diario por el equipo LEAN.</t>
   </si>
   <si>
@@ -217,9 +214,6 @@
     <t>Gestión de Procesos</t>
   </si>
   <si>
-    <t>Plataforma para la automatización y seguimiento de flujos de trabajo, solicitudes y procesos internos del Área LEAN.</t>
-  </si>
-  <si>
     <t>Permite gestionar procesos mediante flujos automatizados.</t>
   </si>
   <si>
@@ -1487,6 +1481,9 @@
   </si>
   <si>
     <t>Las solicitudes deben registrarse con una descripción clara, evidencias (si aplica) y el impacto generado para facilitar su análisis y atención.</t>
+  </si>
+  <si>
+    <t>Plataforma en la que se gestionan y realizan el seguimiento de todos los procesos asociados a un contrato, desde su creación hasta su cierre. Permite visualizar el estado de cada etapa, identificar retrasos y dar trazabilidad a las actividades durante todo el ciclo contractual.</t>
   </si>
 </sst>
 </file>
@@ -2059,13 +2056,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="9" width="25" customWidth="1"/>
+    <col min="1" max="8" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2088,13 +2085,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -2114,27 +2108,24 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
@@ -2143,27 +2134,24 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2172,27 +2160,24 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>468</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2201,27 +2186,24 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2230,27 +2212,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -2259,27 +2238,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2288,27 +2264,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -2317,27 +2290,24 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2346,27 +2316,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2375,27 +2342,24 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2404,25 +2368,22 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2431,25 +2392,22 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2458,25 +2416,22 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2485,25 +2440,22 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2512,25 +2464,22 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2539,25 +2488,22 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2566,25 +2512,22 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2593,12 +2536,9 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="H19" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -2619,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2642,106 +2582,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>362</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>364</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2770,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2793,878 +2733,878 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>429</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B32" t="s">
+        <v>394</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="F32" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="H32" t="s">
+        <v>397</v>
+      </c>
+      <c r="I32" t="s">
         <v>398</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="F32" t="s">
-        <v>287</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="H32" t="s">
-        <v>399</v>
-      </c>
-      <c r="I32" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B33" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H33" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B34" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B35" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F35" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B36" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F36" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B37" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F37" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B38" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B39" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F39" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B40" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F40" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3714,204 +3654,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3957,158 +3897,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4158,45 +4098,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>311</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4204,22 +4144,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4227,33 +4167,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4262,10 +4202,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4273,10 +4213,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4285,10 +4225,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4296,10 +4236,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>347</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4308,10 +4248,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4361,7 +4301,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4375,358 +4315,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>201</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>318</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>216</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>235</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -4782,60 +4722,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9110CCE-2EA8-4B5D-B709-08B9037250AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F11A6E-8A3A-47B0-B587-17D460B8231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,9 +226,6 @@
     <t>Gestión Ágil</t>
   </si>
   <si>
-    <t>Herramienta para la planificación y seguimiento de proyectos mediante metodologías ágiles, facilitando la gestión de tareas y prioridades.</t>
-  </si>
-  <si>
     <t>Utilizada para el seguimiento de desarrollos del área.</t>
   </si>
   <si>
@@ -1484,6 +1481,9 @@
   </si>
   <si>
     <t>Plataforma en la que se gestionan y realizan el seguimiento de todos los procesos asociados a un contrato, desde su creación hasta su cierre. Permite visualizar el estado de cada etapa, identificar retrasos y dar trazabilidad a las actividades durante todo el ciclo contractual.</t>
+  </si>
+  <si>
+    <t>Herramienta para gestionar, priorizar y planificar desarrollos, mediante el registro de historias de usuario y la programación de su ejecución.</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2108,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>35</v>
@@ -2134,7 +2134,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>39</v>
@@ -2151,7 +2151,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2160,10 +2160,10 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2177,7 +2177,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2186,7 +2186,7 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
@@ -2203,7 +2203,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>468</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2212,24 +2212,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -2238,24 +2238,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2264,24 +2264,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -2290,24 +2290,24 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2316,24 +2316,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2342,24 +2342,24 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2368,22 +2368,22 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2392,22 +2392,22 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2416,22 +2416,22 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2440,22 +2440,22 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2464,22 +2464,22 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2488,22 +2488,22 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2512,22 +2512,22 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2536,7 +2536,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2582,106 +2582,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>322</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>323</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>361</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -2710,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2733,760 +2733,760 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>236</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>252</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>260</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>262</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>428</v>
-      </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B31" t="s">
+        <v>393</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>395</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F32" t="s">
+        <v>284</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="H32" t="s">
         <v>396</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F32" t="s">
-        <v>285</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>397</v>
-      </c>
-      <c r="I32" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="F33" t="s">
+        <v>284</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="H33" t="s">
         <v>399</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F33" t="s">
-        <v>285</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="H33" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B34" t="s">
+        <v>400</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B35" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
@@ -3494,22 +3494,22 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B36" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H36" t="s">
         <v>41</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B37" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H37" t="s">
         <v>41</v>
@@ -3540,22 +3540,22 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H38" t="s">
         <v>41</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F39" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H39" t="s">
         <v>41</v>
@@ -3586,22 +3586,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B40" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H40" t="s">
         <v>41</v>
@@ -3654,204 +3654,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -3897,158 +3897,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="G3" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="G4" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="G5" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="G6" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="G7" s="16" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4098,45 +4098,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4144,22 +4144,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>312</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4167,33 +4167,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4202,10 +4202,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="F6" t="s">
         <v>337</v>
-      </c>
-      <c r="F6" t="s">
-        <v>338</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4225,10 +4225,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4248,10 +4248,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4301,7 +4301,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4315,358 +4315,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>199</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>203</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>208</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>316</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>214</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>216</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>218</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>220</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>318</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>320</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>228</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>233</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -4722,60 +4722,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F11A6E-8A3A-47B0-B587-17D460B8231A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02FF00D-08B6-47BF-A6B3-17D7999E6392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,9 +226,6 @@
     <t>Gestión Ágil</t>
   </si>
   <si>
-    <t>Utilizada para el seguimiento de desarrollos del área.</t>
-  </si>
-  <si>
     <t>HER-006</t>
   </si>
   <si>
@@ -1484,6 +1481,9 @@
   </si>
   <si>
     <t>Herramienta para gestionar, priorizar y planificar desarrollos, mediante el registro de historias de usuario y la programación de su ejecución.</t>
+  </si>
+  <si>
+    <t>Las historias de usuario constituyen el insumo principal para el desarrollo y las pruebas funcionales, ya que documentan el alcance, las reglas de negocio, los criterios de aceptación y las especificaciones requeridas para validar la solución implementada.</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2108,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>35</v>
@@ -2134,7 +2134,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>39</v>
@@ -2151,7 +2151,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2160,10 +2160,10 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2177,7 +2177,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2186,13 +2186,13 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>46</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2212,24 +2212,24 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>49</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -2238,24 +2238,24 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2264,24 +2264,24 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -2290,24 +2290,24 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2316,24 +2316,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2342,24 +2342,24 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2368,22 +2368,22 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2392,22 +2392,22 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2416,22 +2416,22 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2440,22 +2440,22 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2464,22 +2464,22 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2488,22 +2488,22 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2512,22 +2512,22 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2536,7 +2536,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2582,106 +2582,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>321</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>322</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>361</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -2710,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2733,760 +2733,760 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D28" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>427</v>
-      </c>
       <c r="H30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B31" t="s">
+        <v>392</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="D31" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B32" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F32" t="s">
+        <v>283</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="H32" t="s">
         <v>395</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F32" t="s">
-        <v>284</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>396</v>
-      </c>
-      <c r="I32" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="F33" t="s">
+        <v>283</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="H33" t="s">
         <v>398</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="F33" t="s">
-        <v>284</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="H33" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B34" t="s">
+        <v>399</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="D34" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
@@ -3494,22 +3494,22 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B36" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H36" t="s">
         <v>41</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B37" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H37" t="s">
         <v>41</v>
@@ -3540,22 +3540,22 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B38" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H38" t="s">
         <v>41</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B39" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F39" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H39" t="s">
         <v>41</v>
@@ -3586,22 +3586,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B40" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F40" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H40" t="s">
         <v>41</v>
@@ -3654,204 +3654,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3897,158 +3897,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="G3" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G4" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="G5" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="G6" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G7" s="16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4098,45 +4098,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4144,22 +4144,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>311</v>
-      </c>
       <c r="C4" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4167,33 +4167,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4202,10 +4202,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="F6" t="s">
         <v>336</v>
-      </c>
-      <c r="F6" t="s">
-        <v>337</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4225,10 +4225,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4248,10 +4248,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4301,7 +4301,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4315,358 +4315,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>198</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>315</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>213</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>215</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>219</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>317</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>319</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>227</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>232</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -4722,60 +4722,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02FF00D-08B6-47BF-A6B3-17D7999E6392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027744D5-256D-4882-950E-AB16AB789EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,12 +280,6 @@
     <t>Business Intelligence</t>
   </si>
   <si>
-    <t>Plataforma para el análisis y visualización de datos mediante dashboards e indicadores de gestión del Área LEAN.</t>
-  </si>
-  <si>
-    <t>Fuente principal para el seguimiento de indicadores.</t>
-  </si>
-  <si>
     <t>HER-010</t>
   </si>
   <si>
@@ -1484,6 +1478,12 @@
   </si>
   <si>
     <t>Las historias de usuario constituyen el insumo principal para el desarrollo y las pruebas funcionales, ya que documentan el alcance, las reglas de negocio, los criterios de aceptación y las especificaciones requeridas para validar la solución implementada.</t>
+  </si>
+  <si>
+    <t>Herramienta para el análisis de datos y el diseño de propuestas de tableros de control. Los tableros desarrollados sirven como prototipos para su validación y posterior implementación en la herramienta oficial de la compañía</t>
+  </si>
+  <si>
+    <t>Los tableros propuestos se construyen con base en los requerimientos del negocio y son validados con las áreas involucradas antes de su desarrollo e implementación en la plataforma oficial de la compañía.</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2108,7 @@
         <v>34</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>35</v>
@@ -2134,7 +2134,7 @@
         <v>34</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>39</v>
@@ -2151,7 +2151,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2160,10 +2160,10 @@
         <v>34</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2177,7 +2177,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2186,7 +2186,7 @@
         <v>34</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>45</v>
@@ -2203,7 +2203,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2212,10 +2212,10 @@
         <v>34</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2238,7 +2238,7 @@
         <v>34</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>53</v>
@@ -2264,7 +2264,7 @@
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>58</v>
@@ -2290,13 +2290,13 @@
         <v>34</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>64</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>467</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2316,24 +2316,24 @@
         <v>34</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>68</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -2342,24 +2342,24 @@
         <v>34</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2368,22 +2368,22 @@
         <v>34</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2392,22 +2392,22 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2416,22 +2416,22 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2440,22 +2440,22 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2464,22 +2464,22 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H16" s="2"/>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2488,22 +2488,22 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H17" s="2"/>
     </row>
     <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2512,22 +2512,22 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H18" s="2"/>
     </row>
     <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2536,7 +2536,7 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -2559,13 +2559,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -2582,106 +2582,106 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="240" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>358</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>360</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="345" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -2710,10 +2710,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2733,760 +2733,760 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>234</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F26" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F27" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F28" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B32" t="s">
+        <v>390</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F32" t="s">
+        <v>281</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H32" t="s">
+        <v>393</v>
+      </c>
+      <c r="I32" t="s">
         <v>394</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="F32" t="s">
-        <v>283</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="H32" t="s">
-        <v>395</v>
-      </c>
-      <c r="I32" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F33" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H33" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B34" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B35" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F35" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
@@ -3494,22 +3494,22 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B36" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F36" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H36" t="s">
         <v>41</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B37" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H37" t="s">
         <v>41</v>
@@ -3540,22 +3540,22 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B38" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F38" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H38" t="s">
         <v>41</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B39" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F39" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H39" t="s">
         <v>41</v>
@@ -3586,22 +3586,22 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B40" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F40" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H40" t="s">
         <v>41</v>
@@ -3654,204 +3654,204 @@
     </row>
     <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>
@@ -3897,158 +3897,158 @@
     </row>
     <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -4098,45 +4098,45 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>307</v>
-      </c>
       <c r="C3" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G3" s="5">
         <v>46097</v>
@@ -4144,22 +4144,22 @@
     </row>
     <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G4" s="5">
         <v>45757</v>
@@ -4167,33 +4167,33 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4202,10 +4202,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4213,10 +4213,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4225,10 +4225,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>341</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>343</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4248,10 +4248,10 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
@@ -4301,7 +4301,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -4315,358 +4315,358 @@
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>194</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>197</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E4" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>206</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>314</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>212</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>319</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>231</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -4722,60 +4722,60 @@
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027744D5-256D-4882-950E-AB16AB789EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125CFB7C-4874-43F5-BC0C-CCEDEDB5F0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="470">
   <si>
     <t>ID</t>
   </si>
@@ -1399,9 +1399,6 @@
     <t>Sistema ERP corporativo utilizado para consultar información administrativa y operativa relacionada con proyectos, contratos, presupuestos y demás procesos empresariales que apoyan la gestión del Área LEAN.</t>
   </si>
   <si>
-    <t>Herramienta que permite establecer una conexión segura a la red corporativa para acceder de forma remota a aplicaciones, servidores y recursos internos utilizados por el Área LEAN.</t>
-  </si>
-  <si>
     <t>Extensión de captura de pantalla y grabación de video utilizada para documentar incidencias y registrar evidencias funcionales de Analytics, apoyando el proceso de reporte y seguimiento de desarrollos.</t>
   </si>
   <si>
@@ -1484,6 +1481,12 @@
   </si>
   <si>
     <t>Los tableros propuestos se construyen con base en los requerimientos del negocio y son validados con las áreas involucradas antes de su desarrollo e implementación en la plataforma oficial de la compañía.</t>
+  </si>
+  <si>
+    <t>Herramienta que permite acceder al entorno de pruebas, el cual se encuentra alojado en la red de las oficinas de Bucaramanga. Su uso es indispensable para la ejecución y validación de pruebas.</t>
+  </si>
+  <si>
+    <t>Es un requisito para acceder al ambiente de pruebas y realizar la validación funcional de los desarrollos antes de su implementación.</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2154,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2163,7 +2166,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2177,7 +2180,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2203,7 +2206,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2215,7 +2218,7 @@
         <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2307,7 +2310,7 @@
         <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2319,7 +2322,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2356,7 +2359,7 @@
         <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>435</v>
@@ -2380,7 +2383,7 @@
         <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>436</v>
@@ -2404,10 +2407,10 @@
         <v>293</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2428,7 +2431,7 @@
         <v>294</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>437</v>
@@ -2452,7 +2455,7 @@
         <v>295</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>438</v>
@@ -2476,7 +2479,7 @@
         <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>439</v>
@@ -2500,10 +2503,10 @@
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2516,7 +2519,7 @@
       </c>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>301</v>
       </c>
@@ -2524,10 +2527,10 @@
         <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2538,7 +2541,9 @@
       <c r="G19" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>469</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -3793,7 +3798,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -3810,16 +3815,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -3828,21 +3833,21 @@
         <v>283</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -3851,7 +3856,7 @@
         <v>283</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4338,7 +4343,7 @@
         <v>193</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>194</v>
@@ -4396,7 +4401,7 @@
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>191</v>
@@ -4474,7 +4479,7 @@
         <v>207</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>208</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125CFB7C-4874-43F5-BC0C-CCEDEDB5F0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958466F1-D404-4116-AE7B-488E02A83C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <author>tc={D91713CE-9323-4968-8C74-9FAC626CD1BE}</author>
   </authors>
   <commentList>
-    <comment ref="C7" authorId="0" shapeId="0" xr:uid="{D91713CE-9323-4968-8C74-9FAC626CD1BE}">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{D91713CE-9323-4968-8C74-9FAC626CD1BE}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="494">
   <si>
     <t>ID</t>
   </si>
@@ -1060,18 +1060,12 @@
     <t>https://www.iglc.net/Papers</t>
   </si>
   <si>
-    <t>DOC-011</t>
-  </si>
-  <si>
     <t>https://leanconstructionblog.com/espanol/index.html</t>
   </si>
   <si>
     <t>LEAN CONSTRUCTION BLOG</t>
   </si>
   <si>
-    <t>DOC-012</t>
-  </si>
-  <si>
     <t>Blog</t>
   </si>
   <si>
@@ -1487,6 +1481,84 @@
   </si>
   <si>
     <t>Es un requisito para acceder al ambiente de pruebas y realizar la validación funcional de los desarrollos antes de su implementación.</t>
+  </si>
+  <si>
+    <t>DOC-01</t>
+  </si>
+  <si>
+    <t>DOC-02</t>
+  </si>
+  <si>
+    <t>https://institutolean.co/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultoria Lean Colombia </t>
+  </si>
+  <si>
+    <t>Pagina Web</t>
+  </si>
+  <si>
+    <t>DOC-03</t>
+  </si>
+  <si>
+    <t>Diana Milena Rojas</t>
+  </si>
+  <si>
+    <t>Ing Auxiliar de Planeación</t>
+  </si>
+  <si>
+    <t>dmrojas@marval.com.co</t>
+  </si>
+  <si>
+    <t>correo: proyectos@marval.com.co contraseña: LeanBIM2020</t>
+  </si>
+  <si>
+    <t>HER-019</t>
+  </si>
+  <si>
+    <t>Sharepoint</t>
+  </si>
+  <si>
+    <t>(URL): https://grupomarval.sharepoint.com/sites/Lean-BIM/Documentos%20compartidos/Forms/AllItems.aspx</t>
+  </si>
+  <si>
+    <t>Carpeta Compartida</t>
+  </si>
+  <si>
+    <t>Correo: EQUIPOLEAN@marval.com.co / proyectos@marval.com.co</t>
+  </si>
+  <si>
+    <t>HER-020</t>
+  </si>
+  <si>
+    <t>Universidad Marval</t>
+  </si>
+  <si>
+    <t>Marval</t>
+  </si>
+  <si>
+    <t>(URL): https://grupomarval.sharepoint.com/:f:/s/UniversidadMarval77/IgAI-LgxUzASSLVOY9FNoYTBAelWyAqFBatlVGy6UMskfiE?e=CcusLZ</t>
+  </si>
+  <si>
+    <t>Carpeta Compartida ADN LEAN</t>
+  </si>
+  <si>
+    <t>Boton Ayudas Analytics</t>
+  </si>
+  <si>
+    <t>HER-021</t>
+  </si>
+  <si>
+    <t>(URL): https://analytics.app.marval.com.co/portal</t>
+  </si>
+  <si>
+    <t>Plataforma corporativa utilizada como repositorio central para almacenar, organizar y compartir documentación, archivos y recursos del Área LEAN, facilitando el trabajo colaborativo y el acceso a la información.</t>
+  </si>
+  <si>
+    <t>Plataforma de capacitación corporativa utilizada para la formación y consulta de contenidos del Área LEAN, incluyendo el curso ADN LEAN, donde se encuentra la documentación, conceptos y lineamientos relacionados con la metodología y los procesos del área.</t>
+  </si>
+  <si>
+    <t>Módulo de soporte integrado en Analytics que reúne videos, manuales y material de consulta para orientar a los usuarios en el uso de la plataforma, incluyendo la gestión de reuniones, asignación de responsables, creación de restricciones, administración de contratistas y demás funcionalidades del sistema.</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1662,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1631,6 +1703,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2051,7 +2129,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C7" dT="2026-07-14T02:31:29.23" personId="{8B6610E4-F322-4CCC-AE1E-2620D129EB03}" id="{D91713CE-9323-4968-8C74-9FAC626CD1BE}">
+  <threadedComment ref="C8" dT="2026-07-14T02:31:29.23" personId="{8B6610E4-F322-4CCC-AE1E-2620D129EB03}" id="{D91713CE-9323-4968-8C74-9FAC626CD1BE}">
     <text>Consultar programadores sucursal Bogota</text>
   </threadedComment>
 </ThreadedComments>
@@ -2059,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="25" customWidth="1"/>
@@ -2154,7 +2232,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2166,7 +2244,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2180,7 +2258,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2206,7 +2284,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2218,7 +2296,7 @@
         <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2310,7 +2388,7 @@
         <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2322,7 +2400,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2359,10 +2437,10 @@
         <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2383,10 +2461,10 @@
         <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2395,7 +2473,7 @@
         <v>34</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H13" s="2"/>
     </row>
@@ -2407,10 +2485,10 @@
         <v>293</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2419,7 +2497,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H14" s="2"/>
     </row>
@@ -2431,10 +2509,10 @@
         <v>294</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2443,7 +2521,7 @@
         <v>34</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H15" s="2"/>
     </row>
@@ -2455,10 +2533,10 @@
         <v>295</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2467,9 +2545,11 @@
         <v>34</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -2479,10 +2559,10 @@
         <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2491,7 +2571,7 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -2503,10 +2583,10 @@
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2515,7 +2595,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H18" s="2"/>
     </row>
@@ -2527,10 +2607,10 @@
         <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2539,10 +2619,82 @@
         <v>34</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="165" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -2619,7 +2771,7 @@
         <v>318</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>319</v>
@@ -2642,13 +2794,13 @@
         <v>284</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>356</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>358</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2668,13 +2820,13 @@
         <v>285</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2753,10 +2905,10 @@
         <v>278</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2776,10 +2928,10 @@
         <v>278</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2799,10 +2951,10 @@
         <v>278</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2822,10 +2974,10 @@
         <v>279</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2845,10 +2997,10 @@
         <v>280</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2868,10 +3020,10 @@
         <v>280</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2891,10 +3043,10 @@
         <v>278</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2914,10 +3066,10 @@
         <v>278</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2937,10 +3089,10 @@
         <v>279</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2960,10 +3112,10 @@
         <v>280</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2983,10 +3135,10 @@
         <v>280</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3006,10 +3158,10 @@
         <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3029,10 +3181,10 @@
         <v>280</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3052,15 +3204,15 @@
         <v>280</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>85</v>
@@ -3075,15 +3227,15 @@
         <v>278</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>91</v>
@@ -3098,10 +3250,10 @@
         <v>279</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3121,10 +3273,10 @@
         <v>279</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3144,10 +3296,10 @@
         <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3164,10 +3316,10 @@
         <v>232</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3184,10 +3336,10 @@
         <v>232</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3204,10 +3356,10 @@
         <v>260</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -3224,15 +3376,15 @@
         <v>260</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>106</v>
@@ -3244,10 +3396,10 @@
         <v>282</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>100</v>
@@ -3270,7 +3422,7 @@
         <v>281</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>100</v>
@@ -3293,7 +3445,7 @@
         <v>281</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="H26" s="8" t="s">
         <v>100</v>
@@ -3301,7 +3453,7 @@
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B27" t="s">
         <v>101</v>
@@ -3316,7 +3468,7 @@
         <v>281</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H27" s="8" t="s">
         <v>100</v>
@@ -3324,7 +3476,7 @@
     </row>
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B28" t="s">
         <v>103</v>
@@ -3339,7 +3491,7 @@
         <v>281</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>100</v>
@@ -3347,7 +3499,7 @@
     </row>
     <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>108</v>
@@ -3356,10 +3508,10 @@
         <v>282</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>100</v>
@@ -3367,19 +3519,19 @@
     </row>
     <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>282</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H30" t="s">
         <v>100</v>
@@ -3387,33 +3539,33 @@
     </row>
     <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>282</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>423</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B32" t="s">
+        <v>388</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>282</v>
@@ -3422,24 +3574,24 @@
         <v>281</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H32" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="I32" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>282</v>
@@ -3448,41 +3600,41 @@
         <v>281</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H33" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B34" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>282</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B35" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>282</v>
@@ -3491,7 +3643,7 @@
         <v>281</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H35" t="s">
         <v>41</v>
@@ -3499,13 +3651,13 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B36" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>282</v>
@@ -3514,7 +3666,7 @@
         <v>281</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H36" t="s">
         <v>41</v>
@@ -3522,13 +3674,13 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B37" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>282</v>
@@ -3537,7 +3689,7 @@
         <v>281</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H37" t="s">
         <v>41</v>
@@ -3545,13 +3697,13 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>282</v>
@@ -3560,7 +3712,7 @@
         <v>281</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="H38" t="s">
         <v>41</v>
@@ -3568,13 +3720,13 @@
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B39" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>282</v>
@@ -3583,7 +3735,7 @@
         <v>281</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="H39" t="s">
         <v>41</v>
@@ -3591,13 +3743,13 @@
     </row>
     <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B40" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>282</v>
@@ -3606,7 +3758,7 @@
         <v>281</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H40" t="s">
         <v>41</v>
@@ -3798,7 +3950,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -3815,16 +3967,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -3833,21 +3985,21 @@
         <v>283</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -3856,7 +4008,7 @@
         <v>283</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -3964,7 +4116,7 @@
         <v>161</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -4103,7 +4255,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>327</v>
+        <v>468</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>325</v>
@@ -4172,19 +4324,19 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>330</v>
+        <v>469</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>283</v>
@@ -4195,10 +4347,10 @@
     </row>
     <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4207,10 +4359,10 @@
         <v>33</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G6" s="5">
         <v>44697</v>
@@ -4218,10 +4370,10 @@
     </row>
     <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -4230,10 +4382,10 @@
         <v>33</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G7" s="5">
         <v>44697</v>
@@ -4241,10 +4393,10 @@
     </row>
     <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -4253,17 +4405,37 @@
         <v>33</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G8" s="5">
         <v>45757</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E9" s="13"/>
+      <c r="A9" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>470</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="14"/>
@@ -4280,15 +4452,16 @@
     <hyperlink ref="B8" r:id="rId3" display="https://us1.aconex.com/rsrc/20260702.0843/es_ES_DOC/document/view/index.html?ControlledDocument_ID=1353331688403523199&amp;ControlledDocument_projectID=1207968420&amp;VIEW_CD_RETURN_URL=%2FSearchControlledDoc%3FSESSION_SAVE_DOCUMENTNO%3D%26SESSION_SAVE_TITLE%3D%2B%26SESSION_SAVE_REVISION%3D%2B%26SESSION_SAVE_STATUS%3D0%26SESSION_SAVE_TYPE%3D0%26SESSION_SAVE_DISCIPLINE%3Dnull%26SESSION_CREATION_DATE%3Dnull%26SESSION_REVISION_DATE%3Dnull%26SESSION_SAVE_REVIEW_DATE%3Dnull%26SESSION_SAVE_REVIEWED_DATE%3Dnull%26SESSION_SAVE_AUTHOR%3Dnull%26SESSION_SAVE_FILETYPE%3Dnull%26SESSION_REFERENCE%3Dnull%26SESSION_SAVE_FOLDER_PATH%3D%26SESSION_SAVE_ALL_REVS%3Dnull%26SESSION_SAVE_SORT_DIR%3DASC%26SESSION_SAVE_SORT_FIELD%3Ddocno%26SESSION_SHARED_TO%3D-1%26SESSION_LINKED_TO_PUBLIC%3D0" xr:uid="{B33F7C5F-686F-4168-AEFA-38B03829F34C}"/>
     <hyperlink ref="E8" r:id="rId4" xr:uid="{3A60C185-9CFD-414E-8CB5-584B4E40E318}"/>
     <hyperlink ref="E4" r:id="rId5" xr:uid="{F6E3CF0D-17C9-4F23-A241-03FF5ABD0FEF}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{DE50EB6C-3AD1-47C2-8FD8-585F368BE920}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId6"/>
+  <drawing r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.140625" bestFit="1" customWidth="1"/>
@@ -4338,49 +4511,49 @@
         <v>186</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>474</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>194</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>195</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>198</v>
+        <v>456</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>194</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>198</v>
@@ -4392,51 +4565,51 @@
         <v>202</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="B6" s="2" t="s">
-        <v>458</v>
+        <v>198</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="6"/>
+        <v>202</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>200</v>
+      </c>
       <c r="F6" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>310</v>
+        <v>456</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>204</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="E7" s="6"/>
       <c r="F7" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>310</v>
@@ -4448,7 +4621,7 @@
         <v>202</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>201</v>
@@ -4456,7 +4629,7 @@
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>311</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>310</v>
@@ -4468,55 +4641,55 @@
         <v>202</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>312</v>
+        <v>206</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>209</v>
-      </c>
       <c r="B11" s="2" t="s">
-        <v>198</v>
+        <v>456</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>208</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>210</v>
+        <v>187</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>198</v>
@@ -4528,7 +4701,7 @@
         <v>202</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>201</v>
@@ -4536,7 +4709,7 @@
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>198</v>
@@ -4548,7 +4721,7 @@
         <v>202</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>201</v>
@@ -4556,19 +4729,19 @@
     </row>
     <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>202</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>201</v>
@@ -4576,19 +4749,19 @@
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>313</v>
+        <v>215</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>198</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>317</v>
+        <v>217</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>314</v>
+      <c r="E15" s="7" t="s">
+        <v>216</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>201</v>
@@ -4596,7 +4769,7 @@
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>198</v>
@@ -4608,7 +4781,7 @@
         <v>202</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>201</v>
@@ -4616,30 +4789,30 @@
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>219</v>
+        <v>315</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>194</v>
+        <v>317</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>222</v>
+        <v>202</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>316</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>194</v>
@@ -4648,7 +4821,7 @@
         <v>223</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>221</v>
@@ -4656,10 +4829,10 @@
     </row>
     <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>194</v>
@@ -4668,32 +4841,53 @@
         <v>223</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>221</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{6D127C7A-0241-425D-B231-F60B2E4600EF}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{56A53F4A-C728-4814-92D7-ACB4836CFF4D}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{08445C15-FE1C-4B51-A194-D7B5E585B82E}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{46AD3213-A31B-41EB-AD28-481E0BBE70C5}"/>
-    <hyperlink ref="E10" r:id="rId5" xr:uid="{74D9AEC3-C035-4B36-8FE9-C68B874F1A1A}"/>
-    <hyperlink ref="E11" r:id="rId6" xr:uid="{107654C7-D37F-43AF-82FF-CCBBB9FDB7BB}"/>
-    <hyperlink ref="E12" r:id="rId7" xr:uid="{8EA97BD4-2C52-4E17-9C7E-3D7EA4DBB977}"/>
-    <hyperlink ref="E13" r:id="rId8" xr:uid="{169676CE-8DEE-4520-AD59-3462E6E1BDEE}"/>
-    <hyperlink ref="E14" r:id="rId9" xr:uid="{F4AFE894-496C-40BA-8420-F286C5362587}"/>
-    <hyperlink ref="E17" r:id="rId10" xr:uid="{CDCE3A66-99F5-4DAE-9F22-C18BA22C24AA}"/>
-    <hyperlink ref="E18" r:id="rId11" xr:uid="{EB396133-BCED-457C-9CC7-9AE5604EA716}"/>
-    <hyperlink ref="E19" r:id="rId12" xr:uid="{C745C1D7-B2E0-4D1F-B26E-131394B318D0}"/>
-    <hyperlink ref="E9" r:id="rId13" xr:uid="{16E2F44F-59C1-471C-9036-287CFD73F44A}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{C6E0648D-7081-45FA-A71B-475EC6CD6563}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{C51DDD55-81AB-4B15-AD64-CC13CB5A6CCB}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{56A53F4A-C728-4814-92D7-ACB4836CFF4D}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{08445C15-FE1C-4B51-A194-D7B5E585B82E}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{46AD3213-A31B-41EB-AD28-481E0BBE70C5}"/>
+    <hyperlink ref="E11" r:id="rId5" xr:uid="{74D9AEC3-C035-4B36-8FE9-C68B874F1A1A}"/>
+    <hyperlink ref="E12" r:id="rId6" xr:uid="{107654C7-D37F-43AF-82FF-CCBBB9FDB7BB}"/>
+    <hyperlink ref="E13" r:id="rId7" xr:uid="{8EA97BD4-2C52-4E17-9C7E-3D7EA4DBB977}"/>
+    <hyperlink ref="E14" r:id="rId8" xr:uid="{169676CE-8DEE-4520-AD59-3462E6E1BDEE}"/>
+    <hyperlink ref="E15" r:id="rId9" xr:uid="{F4AFE894-496C-40BA-8420-F286C5362587}"/>
+    <hyperlink ref="E18" r:id="rId10" xr:uid="{CDCE3A66-99F5-4DAE-9F22-C18BA22C24AA}"/>
+    <hyperlink ref="E19" r:id="rId11" xr:uid="{EB396133-BCED-457C-9CC7-9AE5604EA716}"/>
+    <hyperlink ref="E20" r:id="rId12" xr:uid="{C745C1D7-B2E0-4D1F-B26E-131394B318D0}"/>
+    <hyperlink ref="E10" r:id="rId13" xr:uid="{16E2F44F-59C1-471C-9036-287CFD73F44A}"/>
+    <hyperlink ref="E16" r:id="rId14" xr:uid="{C6E0648D-7081-45FA-A71B-475EC6CD6563}"/>
+    <hyperlink ref="E17" r:id="rId15" xr:uid="{C51DDD55-81AB-4B15-AD64-CC13CB5A6CCB}"/>
+    <hyperlink ref="E3" r:id="rId16" xr:uid="{CB3603D0-EFAC-472E-8BD4-11C9AF5CC626}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{958466F1-D404-4116-AE7B-488E02A83C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673E6892-994D-4B1F-A16E-BC4D64ED80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -1504,9 +1504,6 @@
     <t>Diana Milena Rojas</t>
   </si>
   <si>
-    <t>Ing Auxiliar de Planeación</t>
-  </si>
-  <si>
     <t>dmrojas@marval.com.co</t>
   </si>
   <si>
@@ -1558,7 +1555,10 @@
     <t>Plataforma de capacitación corporativa utilizada para la formación y consulta de contenidos del Área LEAN, incluyendo el curso ADN LEAN, donde se encuentra la documentación, conceptos y lineamientos relacionados con la metodología y los procesos del área.</t>
   </si>
   <si>
-    <t>Módulo de soporte integrado en Analytics que reúne videos, manuales y material de consulta para orientar a los usuarios en el uso de la plataforma, incluyendo la gestión de reuniones, asignación de responsables, creación de restricciones, administración de contratistas y demás funcionalidades del sistema.</t>
+    <t>Módulo de soporte integrado en Analytics que centraliza videos, manuales y guías de uso para facilitar el aprendizaje de la plataforma y resolver dudas sobre sus funcionalidades, promoviendo la autogestión y el uso adecuado de las herramientas del Área LEAN.</t>
+  </si>
+  <si>
+    <t>Analista de Planeación</t>
   </si>
 </sst>
 </file>
@@ -2548,7 +2548,7 @@
         <v>342</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
@@ -2627,16 +2627,16 @@
     </row>
     <row r="20" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>33</v>
@@ -2645,47 +2645,47 @@
         <v>34</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
@@ -2694,7 +2694,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -2890,151 +2890,151 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>415</v>
+      </c>
+      <c r="B2" t="s">
+        <v>404</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>421</v>
+        <v>403</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" t="s">
+        <v>281</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>359</v>
+        <v>427</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>82</v>
+        <v>416</v>
+      </c>
+      <c r="B3" t="s">
+        <v>406</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>421</v>
+        <v>405</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F3" t="s">
+        <v>281</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>360</v>
+        <v>428</v>
+      </c>
+      <c r="H3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>417</v>
+      </c>
+      <c r="B4" t="s">
+        <v>408</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>421</v>
+        <v>407</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" t="s">
+        <v>281</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>361</v>
+        <v>429</v>
+      </c>
+      <c r="H4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>90</v>
+        <v>418</v>
+      </c>
+      <c r="B5" t="s">
+        <v>410</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>421</v>
+        <v>409</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" t="s">
+        <v>281</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>362</v>
+        <v>430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>419</v>
+      </c>
+      <c r="B6" t="s">
+        <v>412</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>421</v>
+        <v>411</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>363</v>
+        <v>431</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>420</v>
+      </c>
+      <c r="B7" t="s">
+        <v>414</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="F7" t="s">
+        <v>281</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>364</v>
+        <v>432</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>232</v>
@@ -3046,18 +3046,18 @@
         <v>421</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>232</v>
@@ -3069,64 +3069,64 @@
         <v>421</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>232</v>
@@ -3138,18 +3138,18 @@
         <v>421</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>232</v>
@@ -3161,133 +3161,133 @@
         <v>421</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>347</v>
+        <v>247</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>348</v>
+        <v>249</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>232</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>232</v>
@@ -3299,273 +3299,282 @@
         <v>421</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="E20" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="F20" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="E21" s="2" t="s">
+        <v>280</v>
+      </c>
       <c r="F21" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>260</v>
+        <v>232</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>349</v>
+        <v>262</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>282</v>
+        <v>232</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>282</v>
+        <v>232</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>280</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>281</v>
+        <v>421</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>283</v>
+        <v>266</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F26" t="s">
-        <v>281</v>
+        <v>271</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B27" t="s">
+        <v>268</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F27" t="s">
-        <v>281</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F28" t="s">
-        <v>281</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>282</v>
+        <v>277</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>260</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>421</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="H29" s="8" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D30" s="8" t="s">
+    <row r="31" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="F31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B31" t="s">
-        <v>388</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B32" t="s">
-        <v>388</v>
+        <v>276</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>390</v>
+        <v>105</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>282</v>
@@ -3574,24 +3583,21 @@
         <v>281</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="H32" t="s">
-        <v>391</v>
-      </c>
-      <c r="I32" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="B33" t="s">
-        <v>388</v>
+        <v>101</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>393</v>
+        <v>102</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>282</v>
@@ -3600,110 +3606,104 @@
         <v>281</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="H33" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>401</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s">
-        <v>395</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>396</v>
+        <v>104</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>421</v>
+      <c r="F34" t="s">
+        <v>281</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B35" t="s">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>403</v>
+        <v>108</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F35" t="s">
-        <v>281</v>
+      <c r="F35" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="H35" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B36" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F36" t="s">
-        <v>281</v>
+      <c r="F36" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="H36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="B37" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F37" t="s">
-        <v>281</v>
+      <c r="F37" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>429</v>
-      </c>
-      <c r="H37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B38" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>282</v>
@@ -3712,21 +3712,24 @@
         <v>281</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="I38" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>282</v>
@@ -3735,41 +3738,38 @@
         <v>281</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="B40" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F40" t="s">
-        <v>281</v>
+      <c r="F40" s="2" t="s">
+        <v>421</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="H40" t="s">
-        <v>41</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{CBBFCFAD-F2B4-49E6-AFA2-A2E8E2BEFE02}"/>
-    <hyperlink ref="G3:G29" r:id="rId2" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{B39A16E9-AB55-4A33-AF19-64F1A9B41477}"/>
-    <hyperlink ref="G30:G40" r:id="rId3" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{AC1F786A-C574-4F44-A7A1-294557B49834}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{CBBFCFAD-F2B4-49E6-AFA2-A2E8E2BEFE02}"/>
+    <hyperlink ref="G9:G35" r:id="rId2" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{B39A16E9-AB55-4A33-AF19-64F1A9B41477}"/>
+    <hyperlink ref="G36:G46" r:id="rId3" display="https://app.notion.com/p/22bd59e7f3bc811886c3f9cd5df7287c?v=22bd59e7f3bc8148a84a000cc9f601b5" xr:uid="{AC1F786A-C574-4F44-A7A1-294557B49834}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4516,7 +4516,7 @@
         <v>474</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>194</v>
@@ -4525,7 +4525,7 @@
         <v>202</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>201</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673E6892-994D-4B1F-A16E-BC4D64ED80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1419F623-C722-4518-B1DE-830B481E6D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -1253,9 +1253,6 @@
   </si>
   <si>
     <t>Last Planner</t>
-  </si>
-  <si>
-    <t>Crear historia</t>
   </si>
   <si>
     <t>CNC cuando se hace reducción</t>
@@ -2232,7 +2229,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2244,7 +2241,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2258,7 +2255,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2284,7 +2281,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2296,7 +2293,7 @@
         <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2388,7 +2385,7 @@
         <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2400,7 +2397,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2437,10 +2434,10 @@
         <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2461,10 +2458,10 @@
         <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2485,10 +2482,10 @@
         <v>293</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2509,10 +2506,10 @@
         <v>294</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2533,10 +2530,10 @@
         <v>295</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2548,7 +2545,7 @@
         <v>342</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
@@ -2559,10 +2556,10 @@
         <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2583,10 +2580,10 @@
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2607,10 +2604,10 @@
         <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2622,21 +2619,21 @@
         <v>343</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>33</v>
@@ -2645,47 +2642,47 @@
         <v>34</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>483</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
@@ -2694,7 +2691,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -2849,7 +2846,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{124371BC-E72D-4ACB-81AC-BC0F07668931}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -2890,13 +2887,13 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>282</v>
@@ -2905,7 +2902,7 @@
         <v>281</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2" t="s">
         <v>41</v>
@@ -2913,13 +2910,13 @@
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>282</v>
@@ -2928,7 +2925,7 @@
         <v>281</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H3" t="s">
         <v>41</v>
@@ -2936,13 +2933,13 @@
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>282</v>
@@ -2951,7 +2948,7 @@
         <v>281</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H4" t="s">
         <v>41</v>
@@ -2959,13 +2956,13 @@
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>282</v>
@@ -2974,7 +2971,7 @@
         <v>281</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H5" t="s">
         <v>41</v>
@@ -2982,13 +2979,13 @@
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>282</v>
@@ -2997,7 +2994,7 @@
         <v>281</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H6" t="s">
         <v>41</v>
@@ -3005,13 +3002,13 @@
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>282</v>
@@ -3020,7 +3017,7 @@
         <v>281</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H7" t="s">
         <v>41</v>
@@ -3043,10 +3040,13 @@
         <v>278</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>359</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3066,10 +3066,13 @@
         <v>278</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>360</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3089,10 +3092,13 @@
         <v>278</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>361</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3112,10 +3118,13 @@
         <v>279</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>362</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3135,10 +3144,13 @@
         <v>280</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>363</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3158,10 +3170,13 @@
         <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>364</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3181,10 +3196,13 @@
         <v>278</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>365</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3204,10 +3222,13 @@
         <v>278</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>366</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3227,10 +3248,13 @@
         <v>279</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>367</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3250,10 +3274,13 @@
         <v>280</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>368</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3273,10 +3300,13 @@
         <v>280</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>369</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3296,10 +3326,13 @@
         <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>370</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3319,10 +3352,13 @@
         <v>280</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>371</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3342,10 +3378,13 @@
         <v>280</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>372</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3365,10 +3404,13 @@
         <v>278</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>373</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3388,10 +3430,13 @@
         <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>374</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3411,10 +3456,13 @@
         <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>375</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3434,10 +3482,13 @@
         <v>280</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>376</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3453,11 +3504,17 @@
       <c r="D26" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="E26" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F26" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>377</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3473,11 +3530,17 @@
       <c r="D27" s="2" t="s">
         <v>232</v>
       </c>
+      <c r="E27" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F27" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>378</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3493,11 +3556,17 @@
       <c r="D28" s="2" t="s">
         <v>260</v>
       </c>
+      <c r="E28" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F28" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>379</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3513,11 +3582,17 @@
       <c r="D29" s="2" t="s">
         <v>260</v>
       </c>
+      <c r="E29" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F29" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>380</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -3533,8 +3608,11 @@
       <c r="D30" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="E30" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F30" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>381</v>
@@ -3556,6 +3634,9 @@
       <c r="D31" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="E31" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F31" s="2" t="s">
         <v>281</v>
       </c>
@@ -3579,6 +3660,9 @@
       <c r="D32" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E32" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F32" t="s">
         <v>281</v>
       </c>
@@ -3589,7 +3673,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>350</v>
       </c>
@@ -3602,6 +3686,9 @@
       <c r="D33" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E33" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F33" t="s">
         <v>281</v>
       </c>
@@ -3612,7 +3699,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>351</v>
       </c>
@@ -3625,6 +3712,9 @@
       <c r="D34" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E34" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F34" t="s">
         <v>281</v>
       </c>
@@ -3635,18 +3725,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>352</v>
       </c>
+      <c r="B35" s="18" t="s">
+        <v>283</v>
+      </c>
       <c r="C35" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E35" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F35" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>386</v>
@@ -3655,9 +3751,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>283</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>387</v>
@@ -3665,19 +3764,22 @@
       <c r="D36" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E36" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F36" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>421</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>422</v>
       </c>
       <c r="H36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B37" t="s">
         <v>388</v>
@@ -3688,16 +3790,22 @@
       <c r="D37" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E37" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F37" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B38" t="s">
         <v>388</v>
@@ -3708,60 +3816,69 @@
       <c r="D38" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E38" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F38" t="s">
         <v>281</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H38" t="s">
         <v>391</v>
       </c>
-      <c r="I38" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B39" t="s">
         <v>388</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E39" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F39" t="s">
         <v>281</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H39" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B40" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="C40" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E40" s="4" t="s">
+        <v>283</v>
+      </c>
       <c r="F40" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -3950,7 +4067,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -3967,16 +4084,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>449</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -3985,21 +4102,21 @@
         <v>283</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -4008,7 +4125,7 @@
         <v>283</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -4255,7 +4372,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>325</v>
@@ -4324,7 +4441,7 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>328</v>
@@ -4416,19 +4533,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B9" t="s">
+        <v>470</v>
+      </c>
+      <c r="C9" t="s">
         <v>471</v>
-      </c>
-      <c r="C9" t="s">
-        <v>472</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>283</v>
@@ -4513,10 +4630,10 @@
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>194</v>
@@ -4525,7 +4642,7 @@
         <v>202</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>201</v>
@@ -4536,7 +4653,7 @@
         <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>194</v>
@@ -4594,7 +4711,7 @@
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
@@ -4672,7 +4789,7 @@
         <v>207</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>208</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1419F623-C722-4518-B1DE-830B481E6D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9818BB33-FE9C-4CD6-9130-4BC3029CF1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -2898,6 +2898,9 @@
       <c r="D2" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E2" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F2" t="s">
         <v>281</v>
       </c>
@@ -2921,6 +2924,9 @@
       <c r="D3" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E3" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F3" t="s">
         <v>281</v>
       </c>
@@ -2944,6 +2950,9 @@
       <c r="D4" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E4" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F4" t="s">
         <v>281</v>
       </c>
@@ -2967,6 +2976,9 @@
       <c r="D5" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E5" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F5" t="s">
         <v>281</v>
       </c>
@@ -2990,6 +3002,9 @@
       <c r="D6" s="8" t="s">
         <v>282</v>
       </c>
+      <c r="E6" s="10" t="s">
+        <v>283</v>
+      </c>
       <c r="F6" t="s">
         <v>281</v>
       </c>
@@ -3012,6 +3027,9 @@
       </c>
       <c r="D7" s="8" t="s">
         <v>282</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="F7" t="s">
         <v>281</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9818BB33-FE9C-4CD6-9130-4BC3029CF1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E4969F-5012-4F62-AB49-D87127E6FE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -4122,6 +4122,9 @@
       <c r="G8" s="2" t="s">
         <v>446</v>
       </c>
+      <c r="H8" s="4" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
@@ -4144,6 +4147,9 @@
       </c>
       <c r="G9" s="6" t="s">
         <v>454</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E4969F-5012-4F62-AB49-D87127E6FE68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13139D4A-C952-44BD-8A21-F6CA32804A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="Roadmap" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -77,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -2419,7 +2418,7 @@
       <c r="F11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="4" t="s">
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -2448,7 +2447,9 @@
       <c r="G12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -2472,7 +2473,9 @@
       <c r="G13" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="H13" s="2"/>
+      <c r="H13" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -2496,7 +2499,9 @@
       <c r="G14" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -2520,7 +2525,9 @@
       <c r="G15" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -2570,7 +2577,9 @@
       <c r="G17" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -2594,7 +2603,9 @@
       <c r="G18" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
@@ -2670,6 +2681,9 @@
       <c r="G21" s="2" t="s">
         <v>484</v>
       </c>
+      <c r="H21" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -2692,6 +2706,9 @@
       </c>
       <c r="G22" s="2" t="s">
         <v>488</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13139D4A-C952-44BD-8A21-F6CA32804A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C668591D-673A-410E-92B6-003B22B21B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="492">
   <si>
     <t>ID</t>
   </si>
@@ -1105,9 +1105,6 @@
   </si>
   <si>
     <t>(URL): https://www.youtube.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(URL): </t>
   </si>
   <si>
     <t>(URL): https://produccion.jde.marval.com.co/jde/E1Menu.maf</t>
@@ -2228,7 +2225,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2240,7 +2237,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="180" x14ac:dyDescent="0.25">
@@ -2254,7 +2251,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2280,7 +2277,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -2292,7 +2289,7 @@
         <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2384,7 +2381,7 @@
         <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -2396,7 +2393,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="105" x14ac:dyDescent="0.25">
@@ -2433,10 +2430,10 @@
         <v>291</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -2444,8 +2441,8 @@
       <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>81</v>
+      <c r="G12" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>71</v>
@@ -2459,10 +2456,10 @@
         <v>292</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -2485,10 +2482,10 @@
         <v>293</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -2497,7 +2494,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>71</v>
@@ -2511,10 +2508,10 @@
         <v>294</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -2537,10 +2534,10 @@
         <v>295</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -2552,7 +2549,7 @@
         <v>342</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
@@ -2563,10 +2560,10 @@
         <v>296</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -2575,7 +2572,7 @@
         <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>71</v>
@@ -2589,10 +2586,10 @@
         <v>299</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -2601,7 +2598,7 @@
         <v>34</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>71</v>
@@ -2615,10 +2612,10 @@
         <v>300</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -2626,25 +2623,25 @@
       <c r="F19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>343</v>
+      <c r="G19" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>33</v>
@@ -2653,33 +2650,33 @@
         <v>34</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>71</v>
@@ -2687,16 +2684,16 @@
     </row>
     <row r="22" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
@@ -2705,7 +2702,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>71</v>
@@ -2785,7 +2782,7 @@
         <v>318</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>319</v>
@@ -2808,13 +2805,13 @@
         <v>284</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>356</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -2834,13 +2831,13 @@
         <v>285</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -2904,13 +2901,13 @@
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>282</v>
@@ -2922,7 +2919,7 @@
         <v>281</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2" t="s">
         <v>41</v>
@@ -2930,13 +2927,13 @@
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>282</v>
@@ -2948,7 +2945,7 @@
         <v>281</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H3" t="s">
         <v>41</v>
@@ -2956,13 +2953,13 @@
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>282</v>
@@ -2974,7 +2971,7 @@
         <v>281</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H4" t="s">
         <v>41</v>
@@ -2982,13 +2979,13 @@
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>282</v>
@@ -3000,7 +2997,7 @@
         <v>281</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H5" t="s">
         <v>41</v>
@@ -3008,13 +3005,13 @@
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>282</v>
@@ -3026,7 +3023,7 @@
         <v>281</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H6" t="s">
         <v>41</v>
@@ -3034,13 +3031,13 @@
     </row>
     <row r="7" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>282</v>
@@ -3052,7 +3049,7 @@
         <v>281</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H7" t="s">
         <v>41</v>
@@ -3075,10 +3072,10 @@
         <v>278</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>283</v>
@@ -3101,10 +3098,10 @@
         <v>278</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>283</v>
@@ -3127,10 +3124,10 @@
         <v>278</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>283</v>
@@ -3153,10 +3150,10 @@
         <v>279</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>283</v>
@@ -3179,10 +3176,10 @@
         <v>280</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>283</v>
@@ -3205,10 +3202,10 @@
         <v>280</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>283</v>
@@ -3231,10 +3228,10 @@
         <v>278</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>283</v>
@@ -3257,10 +3254,10 @@
         <v>278</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>283</v>
@@ -3283,10 +3280,10 @@
         <v>279</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>283</v>
@@ -3309,10 +3306,10 @@
         <v>280</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>283</v>
@@ -3335,10 +3332,10 @@
         <v>280</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>283</v>
@@ -3361,10 +3358,10 @@
         <v>280</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>283</v>
@@ -3387,10 +3384,10 @@
         <v>280</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>283</v>
@@ -3413,10 +3410,10 @@
         <v>280</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>283</v>
@@ -3424,7 +3421,7 @@
     </row>
     <row r="22" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>85</v>
@@ -3439,10 +3436,10 @@
         <v>278</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>283</v>
@@ -3450,7 +3447,7 @@
     </row>
     <row r="23" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>91</v>
@@ -3465,10 +3462,10 @@
         <v>279</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>283</v>
@@ -3491,10 +3488,10 @@
         <v>279</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>283</v>
@@ -3517,10 +3514,10 @@
         <v>280</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>283</v>
@@ -3543,10 +3540,10 @@
         <v>283</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>283</v>
@@ -3569,10 +3566,10 @@
         <v>283</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>283</v>
@@ -3595,10 +3592,10 @@
         <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>283</v>
@@ -3621,10 +3618,10 @@
         <v>283</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>283</v>
@@ -3632,7 +3629,7 @@
     </row>
     <row r="30" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>106</v>
@@ -3647,10 +3644,10 @@
         <v>283</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>100</v>
@@ -3676,7 +3673,7 @@
         <v>281</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>100</v>
@@ -3702,7 +3699,7 @@
         <v>281</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H32" s="8" t="s">
         <v>100</v>
@@ -3710,7 +3707,7 @@
     </row>
     <row r="33" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s">
         <v>101</v>
@@ -3728,7 +3725,7 @@
         <v>281</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>100</v>
@@ -3736,7 +3733,7 @@
     </row>
     <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s">
         <v>103</v>
@@ -3754,7 +3751,7 @@
         <v>281</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>100</v>
@@ -3762,7 +3759,7 @@
     </row>
     <row r="35" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>283</v>
@@ -3777,10 +3774,10 @@
         <v>283</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>100</v>
@@ -3788,13 +3785,13 @@
     </row>
     <row r="36" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>283</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>282</v>
@@ -3803,10 +3800,10 @@
         <v>283</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>420</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>421</v>
       </c>
       <c r="H36" t="s">
         <v>100</v>
@@ -3814,13 +3811,13 @@
     </row>
     <row r="37" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B37" t="s">
+        <v>387</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>282</v>
@@ -3829,10 +3826,10 @@
         <v>283</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>283</v>
@@ -3840,13 +3837,13 @@
     </row>
     <row r="38" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>282</v>
@@ -3858,21 +3855,21 @@
         <v>281</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>282</v>
@@ -3884,21 +3881,21 @@
         <v>281</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H39" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s">
+        <v>393</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>282</v>
@@ -3907,10 +3904,10 @@
         <v>283</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>283</v>
@@ -4102,7 +4099,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -4119,16 +4116,16 @@
     </row>
     <row r="8" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -4137,7 +4134,7 @@
         <v>283</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>283</v>
@@ -4145,16 +4142,16 @@
     </row>
     <row r="9" spans="1:8" ht="210" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -4163,7 +4160,7 @@
         <v>283</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>283</v>
@@ -4413,7 +4410,7 @@
     </row>
     <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>325</v>
@@ -4482,7 +4479,7 @@
     </row>
     <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>328</v>
@@ -4574,19 +4571,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C9" t="s">
         <v>470</v>
-      </c>
-      <c r="C9" t="s">
-        <v>471</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>283</v>
@@ -4671,10 +4668,10 @@
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>194</v>
@@ -4683,7 +4680,7 @@
         <v>202</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>201</v>
@@ -4694,7 +4691,7 @@
         <v>193</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>194</v>
@@ -4752,7 +4749,7 @@
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>191</v>
@@ -4830,7 +4827,7 @@
         <v>207</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>208</v>

--- a/data/Centro_Conocimiento_LEAN.xlsx
+++ b/data/Centro_Conocimiento_LEAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dpherrera\Documents\CentroConocimientoLEAN\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C668591D-673A-410E-92B6-003B22B21B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23BF952-6358-4F5E-A3F3-77EEEA120A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herramientas" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -1552,6 +1552,9 @@
   </si>
   <si>
     <t>Analista de Planeación</t>
+  </si>
+  <si>
+    <t>https://us1.aconex.com/ViewDoc?trackingid=1353331688098791834&amp;projectid=1207968420&amp;cversion=1&amp;tab=1</t>
   </si>
 </sst>
 </file>
@@ -4226,7 +4229,9 @@
       <c r="F2" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="16" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -4362,18 +4367,22 @@
       <c r="F8" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="4" t="s">
+        <v>283</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" xr:uid="{E450CA4A-B2D1-4690-B3E1-010CCC902B44}"/>
     <hyperlink ref="G6" r:id="rId2" xr:uid="{95B4B31C-CB0B-4481-8BDB-D15000630CDB}"/>
     <hyperlink ref="G4" r:id="rId3" xr:uid="{1304D265-C734-41FD-B0DC-79EE4DF3EB3C}"/>
     <hyperlink ref="G5" r:id="rId4" xr:uid="{7859DA98-00F2-428D-8A15-DBB023397F25}"/>
     <hyperlink ref="G7" r:id="rId5" xr:uid="{0F00771F-5197-40C4-8FA1-598441B6B712}"/>
+    <hyperlink ref="G2" r:id="rId6" display="https://us1.aconex.com/ViewDoc?trackingid=1353331688098791834&amp;projectid=1207968420&amp;cversion=1&amp;tab=0" xr:uid="{679F82E8-C192-41F6-8413-7DF0B4106B37}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId6"/>
+  <legacyDrawing r:id="rId7"/>
 </worksheet>
 </file>
 
